--- a/datasets/xlsx/CSPreMatchStatistics.xlsx
+++ b/datasets/xlsx/CSPreMatchStatistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AC8012-7F40-4919-9DC7-EA4ABDE26C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE35677F-F299-4827-9A24-1048525493F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="7965" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="7935" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T136"/>
+  <dimension ref="A1:T146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -8332,6 +8332,507 @@
         <v>10</v>
       </c>
     </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>897</v>
+      </c>
+      <c r="B138">
+        <v>11111</v>
+      </c>
+      <c r="C138">
+        <v>5</v>
+      </c>
+      <c r="D138">
+        <v>16919</v>
+      </c>
+      <c r="E138">
+        <v>16553</v>
+      </c>
+      <c r="F138">
+        <v>16492</v>
+      </c>
+      <c r="G138">
+        <v>15766</v>
+      </c>
+      <c r="H138">
+        <v>15114</v>
+      </c>
+      <c r="I138">
+        <v>19459</v>
+      </c>
+      <c r="J138">
+        <v>15333</v>
+      </c>
+      <c r="K138">
+        <v>15959</v>
+      </c>
+      <c r="L138">
+        <v>12660</v>
+      </c>
+      <c r="M138">
+        <v>10844</v>
+      </c>
+      <c r="N138">
+        <v>-1</v>
+      </c>
+      <c r="O138">
+        <v>-4</v>
+      </c>
+      <c r="P138">
+        <v>-3</v>
+      </c>
+      <c r="Q138">
+        <v>-2</v>
+      </c>
+      <c r="R138">
+        <v>10</v>
+      </c>
+      <c r="S138">
+        <v>3</v>
+      </c>
+      <c r="T138">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>898</v>
+      </c>
+      <c r="B139">
+        <v>311</v>
+      </c>
+      <c r="C139">
+        <v>2111</v>
+      </c>
+      <c r="D139">
+        <v>16032</v>
+      </c>
+      <c r="E139">
+        <v>15897</v>
+      </c>
+      <c r="F139">
+        <v>17082</v>
+      </c>
+      <c r="G139">
+        <v>14689</v>
+      </c>
+      <c r="H139">
+        <v>12581</v>
+      </c>
+      <c r="I139">
+        <v>15519</v>
+      </c>
+      <c r="J139">
+        <v>15966</v>
+      </c>
+      <c r="K139">
+        <v>15246</v>
+      </c>
+      <c r="M139">
+        <v>18101</v>
+      </c>
+      <c r="N139">
+        <v>-4</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>3</v>
+      </c>
+      <c r="Q139">
+        <v>5</v>
+      </c>
+      <c r="R139">
+        <v>-3</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>899</v>
+      </c>
+      <c r="B140">
+        <v>2111</v>
+      </c>
+      <c r="C140">
+        <v>5</v>
+      </c>
+      <c r="D140">
+        <v>16374</v>
+      </c>
+      <c r="E140">
+        <v>15726</v>
+      </c>
+      <c r="F140">
+        <v>15598</v>
+      </c>
+      <c r="G140">
+        <v>12475</v>
+      </c>
+      <c r="H140">
+        <v>17262</v>
+      </c>
+      <c r="I140">
+        <v>8439</v>
+      </c>
+      <c r="J140">
+        <v>12872</v>
+      </c>
+      <c r="K140">
+        <v>22269</v>
+      </c>
+      <c r="L140">
+        <v>8772</v>
+      </c>
+      <c r="M140">
+        <v>8030</v>
+      </c>
+      <c r="N140">
+        <v>-7</v>
+      </c>
+      <c r="O140">
+        <v>-1</v>
+      </c>
+      <c r="P140">
+        <v>6</v>
+      </c>
+      <c r="Q140">
+        <v>3</v>
+      </c>
+      <c r="R140">
+        <v>7</v>
+      </c>
+      <c r="S140">
+        <v>-2</v>
+      </c>
+      <c r="T140">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>900</v>
+      </c>
+      <c r="B141">
+        <v>5</v>
+      </c>
+      <c r="C141">
+        <v>311</v>
+      </c>
+      <c r="D141">
+        <v>23189</v>
+      </c>
+      <c r="E141">
+        <v>16585</v>
+      </c>
+      <c r="G141">
+        <v>25466</v>
+      </c>
+      <c r="H141">
+        <v>19226</v>
+      </c>
+      <c r="J141">
+        <v>23398</v>
+      </c>
+      <c r="K141">
+        <v>19855</v>
+      </c>
+      <c r="M141">
+        <v>20469</v>
+      </c>
+      <c r="N141">
+        <v>-9</v>
+      </c>
+      <c r="O141">
+        <v>2</v>
+      </c>
+      <c r="P141">
+        <v>-3</v>
+      </c>
+      <c r="Q141">
+        <v>6</v>
+      </c>
+      <c r="R141">
+        <v>-7</v>
+      </c>
+      <c r="S141">
+        <v>10</v>
+      </c>
+      <c r="T141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>901</v>
+      </c>
+      <c r="B142">
+        <v>2111</v>
+      </c>
+      <c r="C142">
+        <v>221</v>
+      </c>
+      <c r="F142">
+        <v>14523</v>
+      </c>
+      <c r="G142">
+        <v>17252</v>
+      </c>
+      <c r="H142">
+        <v>16926</v>
+      </c>
+      <c r="I142">
+        <v>17810</v>
+      </c>
+      <c r="J142">
+        <v>16622</v>
+      </c>
+      <c r="K142">
+        <v>18991</v>
+      </c>
+      <c r="L142">
+        <v>14999</v>
+      </c>
+      <c r="M142">
+        <v>16383</v>
+      </c>
+      <c r="N142">
+        <v>-1</v>
+      </c>
+      <c r="O142">
+        <v>-10</v>
+      </c>
+      <c r="P142">
+        <v>-1</v>
+      </c>
+      <c r="Q142">
+        <v>6</v>
+      </c>
+      <c r="R142">
+        <v>6</v>
+      </c>
+      <c r="S142">
+        <v>-4</v>
+      </c>
+      <c r="T142">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>902</v>
+      </c>
+      <c r="B143">
+        <v>311</v>
+      </c>
+      <c r="C143">
+        <v>2111</v>
+      </c>
+      <c r="D143">
+        <v>16142</v>
+      </c>
+      <c r="E143">
+        <v>17234</v>
+      </c>
+      <c r="F143">
+        <v>16346</v>
+      </c>
+      <c r="G143">
+        <v>12612</v>
+      </c>
+      <c r="I143">
+        <v>17736</v>
+      </c>
+      <c r="J143">
+        <v>17198</v>
+      </c>
+      <c r="K143">
+        <v>16300</v>
+      </c>
+      <c r="N143">
+        <v>6</v>
+      </c>
+      <c r="O143">
+        <v>5</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>2</v>
+      </c>
+      <c r="R143">
+        <v>-5</v>
+      </c>
+      <c r="S143">
+        <v>-9</v>
+      </c>
+      <c r="T143">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>903</v>
+      </c>
+      <c r="B144">
+        <v>41</v>
+      </c>
+      <c r="C144">
+        <v>5</v>
+      </c>
+      <c r="D144">
+        <v>23333</v>
+      </c>
+      <c r="F144">
+        <v>15982</v>
+      </c>
+      <c r="G144">
+        <v>17586</v>
+      </c>
+      <c r="H144">
+        <v>19112</v>
+      </c>
+      <c r="I144">
+        <v>20576</v>
+      </c>
+      <c r="J144">
+        <v>23374</v>
+      </c>
+      <c r="K144">
+        <v>18351</v>
+      </c>
+      <c r="L144">
+        <v>11748</v>
+      </c>
+      <c r="N144">
+        <v>-3</v>
+      </c>
+      <c r="O144">
+        <v>4</v>
+      </c>
+      <c r="P144">
+        <v>-1</v>
+      </c>
+      <c r="Q144">
+        <v>8</v>
+      </c>
+      <c r="R144">
+        <v>-2</v>
+      </c>
+      <c r="S144">
+        <v>-4</v>
+      </c>
+      <c r="T144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>904</v>
+      </c>
+      <c r="B145">
+        <v>2111</v>
+      </c>
+      <c r="C145">
+        <v>2111</v>
+      </c>
+      <c r="F145">
+        <v>13781</v>
+      </c>
+      <c r="K145">
+        <v>9999</v>
+      </c>
+      <c r="L145">
+        <v>9552</v>
+      </c>
+      <c r="N145">
+        <v>3</v>
+      </c>
+      <c r="O145">
+        <v>-1</v>
+      </c>
+      <c r="P145">
+        <v>1</v>
+      </c>
+      <c r="Q145">
+        <v>14</v>
+      </c>
+      <c r="R145">
+        <v>-1</v>
+      </c>
+      <c r="S145">
+        <v>1</v>
+      </c>
+      <c r="T145">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>905</v>
+      </c>
+      <c r="B146">
+        <v>41</v>
+      </c>
+      <c r="C146">
+        <v>2111</v>
+      </c>
+      <c r="D146">
+        <v>17921</v>
+      </c>
+      <c r="E146">
+        <v>16416</v>
+      </c>
+      <c r="F146">
+        <v>14999</v>
+      </c>
+      <c r="G146">
+        <v>14452</v>
+      </c>
+      <c r="H146">
+        <v>16725</v>
+      </c>
+      <c r="I146">
+        <v>16979</v>
+      </c>
+      <c r="J146">
+        <v>16561</v>
+      </c>
+      <c r="L146">
+        <v>16742</v>
+      </c>
+      <c r="M146">
+        <v>15318</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>5</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>4</v>
+      </c>
+      <c r="R146">
+        <v>-5</v>
+      </c>
+      <c r="S146">
+        <v>7</v>
+      </c>
+      <c r="T146">
+        <v>-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datasets/xlsx/CSPreMatchStatistics.xlsx
+++ b/datasets/xlsx/CSPreMatchStatistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE35677F-F299-4827-9A24-1048525493F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08758215-5FB8-411D-8C9A-DAF79B6E70FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7935" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -146,13 +146,24 @@
   <si>
     <t>Always be the biggest number first.</t>
   </si>
+  <si>
+    <t>AnubisDiff</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -180,8 +191,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T146"/>
+  <dimension ref="A1:U239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -480,9 +492,10 @@
     <col min="17" max="17" width="9.5703125" customWidth="1"/>
     <col min="19" max="19" width="11.7109375" customWidth="1"/>
     <col min="20" max="20" width="12.85546875" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -543,8 +556,11 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>744</v>
       </c>
@@ -588,7 +604,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>745</v>
       </c>
@@ -629,7 +645,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>750</v>
       </c>
@@ -679,7 +695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>752</v>
       </c>
@@ -735,7 +751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>753</v>
       </c>
@@ -794,7 +810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>754</v>
       </c>
@@ -850,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>755</v>
       </c>
@@ -906,7 +922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>756</v>
       </c>
@@ -962,7 +978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>757</v>
       </c>
@@ -1006,7 +1022,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>758</v>
       </c>
@@ -1047,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>759</v>
       </c>
@@ -1100,7 +1116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>760</v>
       </c>
@@ -1156,7 +1172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>761</v>
       </c>
@@ -1218,7 +1234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>762</v>
       </c>
@@ -1271,7 +1287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>763</v>
       </c>
@@ -8332,346 +8348,402 @@
         <v>10</v>
       </c>
     </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>897</v>
+      </c>
+      <c r="B137">
+        <v>11111</v>
+      </c>
+      <c r="C137">
+        <v>5</v>
+      </c>
+      <c r="D137">
+        <v>16919</v>
+      </c>
+      <c r="E137">
+        <v>16553</v>
+      </c>
+      <c r="F137">
+        <v>16492</v>
+      </c>
+      <c r="G137">
+        <v>15766</v>
+      </c>
+      <c r="H137">
+        <v>15114</v>
+      </c>
+      <c r="I137">
+        <v>19459</v>
+      </c>
+      <c r="J137">
+        <v>15333</v>
+      </c>
+      <c r="K137">
+        <v>15959</v>
+      </c>
+      <c r="L137">
+        <v>12660</v>
+      </c>
+      <c r="M137">
+        <v>10844</v>
+      </c>
+      <c r="N137">
+        <v>-1</v>
+      </c>
+      <c r="O137">
+        <v>-4</v>
+      </c>
+      <c r="P137">
+        <v>-3</v>
+      </c>
+      <c r="Q137">
+        <v>-2</v>
+      </c>
+      <c r="R137">
+        <v>10</v>
+      </c>
+      <c r="S137">
+        <v>3</v>
+      </c>
+      <c r="T137">
+        <v>-3</v>
+      </c>
+    </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B138">
-        <v>11111</v>
+        <v>311</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>2111</v>
       </c>
       <c r="D138">
-        <v>16919</v>
+        <v>16032</v>
       </c>
       <c r="E138">
-        <v>16553</v>
+        <v>15897</v>
       </c>
       <c r="F138">
-        <v>16492</v>
+        <v>17082</v>
       </c>
       <c r="G138">
-        <v>15766</v>
+        <v>14689</v>
       </c>
       <c r="H138">
-        <v>15114</v>
+        <v>12581</v>
       </c>
       <c r="I138">
-        <v>19459</v>
+        <v>15519</v>
       </c>
       <c r="J138">
-        <v>15333</v>
+        <v>15966</v>
       </c>
       <c r="K138">
-        <v>15959</v>
-      </c>
-      <c r="L138">
-        <v>12660</v>
+        <v>15246</v>
       </c>
       <c r="M138">
-        <v>10844</v>
+        <v>18101</v>
       </c>
       <c r="N138">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="O138">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P138">
+        <v>3</v>
+      </c>
+      <c r="Q138">
+        <v>5</v>
+      </c>
+      <c r="R138">
         <v>-3</v>
       </c>
-      <c r="Q138">
-        <v>-2</v>
-      </c>
-      <c r="R138">
-        <v>10</v>
-      </c>
       <c r="S138">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T138">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B139">
-        <v>311</v>
+        <v>2111</v>
       </c>
       <c r="C139">
-        <v>2111</v>
+        <v>5</v>
       </c>
       <c r="D139">
-        <v>16032</v>
+        <v>16374</v>
       </c>
       <c r="E139">
-        <v>15897</v>
+        <v>15726</v>
       </c>
       <c r="F139">
-        <v>17082</v>
+        <v>15598</v>
       </c>
       <c r="G139">
-        <v>14689</v>
+        <v>12475</v>
       </c>
       <c r="H139">
-        <v>12581</v>
+        <v>17262</v>
       </c>
       <c r="I139">
-        <v>15519</v>
+        <v>8439</v>
       </c>
       <c r="J139">
-        <v>15966</v>
+        <v>12872</v>
       </c>
       <c r="K139">
-        <v>15246</v>
+        <v>22269</v>
+      </c>
+      <c r="L139">
+        <v>8772</v>
       </c>
       <c r="M139">
-        <v>18101</v>
+        <v>8030</v>
       </c>
       <c r="N139">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P139">
+        <v>6</v>
+      </c>
+      <c r="Q139">
         <v>3</v>
       </c>
-      <c r="Q139">
-        <v>5</v>
-      </c>
       <c r="R139">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T139">
-        <v>2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B140">
-        <v>2111</v>
+        <v>5</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <v>311</v>
       </c>
       <c r="D140">
-        <v>16374</v>
+        <v>23189</v>
       </c>
       <c r="E140">
-        <v>15726</v>
-      </c>
-      <c r="F140">
-        <v>15598</v>
+        <v>16585</v>
       </c>
       <c r="G140">
-        <v>12475</v>
+        <v>25466</v>
       </c>
       <c r="H140">
-        <v>17262</v>
-      </c>
-      <c r="I140">
-        <v>8439</v>
+        <v>19226</v>
       </c>
       <c r="J140">
-        <v>12872</v>
+        <v>23398</v>
       </c>
       <c r="K140">
-        <v>22269</v>
-      </c>
-      <c r="L140">
-        <v>8772</v>
+        <v>19855</v>
       </c>
       <c r="M140">
-        <v>8030</v>
+        <v>20469</v>
       </c>
       <c r="N140">
+        <v>-9</v>
+      </c>
+      <c r="O140">
+        <v>2</v>
+      </c>
+      <c r="P140">
+        <v>-3</v>
+      </c>
+      <c r="Q140">
+        <v>6</v>
+      </c>
+      <c r="R140">
         <v>-7</v>
       </c>
-      <c r="O140">
-        <v>-1</v>
-      </c>
-      <c r="P140">
-        <v>6</v>
-      </c>
-      <c r="Q140">
-        <v>3</v>
-      </c>
-      <c r="R140">
-        <v>7</v>
-      </c>
       <c r="S140">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="T140">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B141">
-        <v>5</v>
+        <v>2111</v>
       </c>
       <c r="C141">
-        <v>311</v>
-      </c>
-      <c r="D141">
-        <v>23189</v>
-      </c>
-      <c r="E141">
-        <v>16585</v>
+        <v>221</v>
+      </c>
+      <c r="F141">
+        <v>14523</v>
       </c>
       <c r="G141">
-        <v>25466</v>
+        <v>17252</v>
       </c>
       <c r="H141">
-        <v>19226</v>
+        <v>16926</v>
+      </c>
+      <c r="I141">
+        <v>17810</v>
       </c>
       <c r="J141">
-        <v>23398</v>
+        <v>16622</v>
       </c>
       <c r="K141">
-        <v>19855</v>
+        <v>18991</v>
+      </c>
+      <c r="L141">
+        <v>14999</v>
       </c>
       <c r="M141">
-        <v>20469</v>
+        <v>16383</v>
       </c>
       <c r="N141">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="O141">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="P141">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="Q141">
         <v>6</v>
       </c>
       <c r="R141">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="S141">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="T141">
-        <v>1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B142">
+        <v>311</v>
+      </c>
+      <c r="C142">
         <v>2111</v>
       </c>
-      <c r="C142">
-        <v>221</v>
+      <c r="D142">
+        <v>16142</v>
+      </c>
+      <c r="E142">
+        <v>17234</v>
       </c>
       <c r="F142">
-        <v>14523</v>
+        <v>16346</v>
       </c>
       <c r="G142">
-        <v>17252</v>
-      </c>
-      <c r="H142">
-        <v>16926</v>
+        <v>12612</v>
       </c>
       <c r="I142">
-        <v>17810</v>
+        <v>17736</v>
       </c>
       <c r="J142">
-        <v>16622</v>
+        <v>17198</v>
       </c>
       <c r="K142">
-        <v>18991</v>
-      </c>
-      <c r="L142">
-        <v>14999</v>
-      </c>
-      <c r="M142">
-        <v>16383</v>
+        <v>16300</v>
       </c>
       <c r="N142">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O142">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="P142">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R142">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="S142">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="T142">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B143">
-        <v>311</v>
+        <v>41</v>
       </c>
       <c r="C143">
-        <v>2111</v>
+        <v>5</v>
       </c>
       <c r="D143">
-        <v>16142</v>
-      </c>
-      <c r="E143">
-        <v>17234</v>
+        <v>23333</v>
       </c>
       <c r="F143">
-        <v>16346</v>
+        <v>15982</v>
       </c>
       <c r="G143">
-        <v>12612</v>
+        <v>17586</v>
+      </c>
+      <c r="H143">
+        <v>19112</v>
       </c>
       <c r="I143">
-        <v>17736</v>
+        <v>20576</v>
       </c>
       <c r="J143">
-        <v>17198</v>
+        <v>23374</v>
       </c>
       <c r="K143">
-        <v>16300</v>
+        <v>18351</v>
+      </c>
+      <c r="L143">
+        <v>11748</v>
       </c>
       <c r="N143">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="O143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q143">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R143">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="S143">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="T143">
         <v>4</v>
@@ -8679,158 +8751,3816 @@
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B144">
-        <v>41</v>
+        <v>2111</v>
       </c>
       <c r="C144">
-        <v>5</v>
-      </c>
-      <c r="D144">
-        <v>23333</v>
+        <v>2111</v>
       </c>
       <c r="F144">
-        <v>15982</v>
-      </c>
-      <c r="G144">
-        <v>17586</v>
-      </c>
-      <c r="H144">
-        <v>19112</v>
-      </c>
-      <c r="I144">
-        <v>20576</v>
-      </c>
-      <c r="J144">
-        <v>23374</v>
+        <v>13781</v>
       </c>
       <c r="K144">
-        <v>18351</v>
+        <v>9999</v>
       </c>
       <c r="L144">
-        <v>11748</v>
+        <v>9552</v>
       </c>
       <c r="N144">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O144">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="P144">
+        <v>1</v>
+      </c>
+      <c r="Q144">
+        <v>14</v>
+      </c>
+      <c r="R144">
         <v>-1</v>
       </c>
-      <c r="Q144">
-        <v>8</v>
-      </c>
-      <c r="R144">
-        <v>-2</v>
-      </c>
       <c r="S144">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="T144">
-        <v>4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B145">
-        <v>2111</v>
+        <v>41</v>
       </c>
       <c r="C145">
         <v>2111</v>
       </c>
+      <c r="D145">
+        <v>17921</v>
+      </c>
+      <c r="E145">
+        <v>16416</v>
+      </c>
       <c r="F145">
-        <v>13781</v>
-      </c>
-      <c r="K145">
-        <v>9999</v>
+        <v>14999</v>
+      </c>
+      <c r="G145">
+        <v>14452</v>
+      </c>
+      <c r="H145">
+        <v>16725</v>
+      </c>
+      <c r="I145">
+        <v>16979</v>
+      </c>
+      <c r="J145">
+        <v>16561</v>
       </c>
       <c r="L145">
-        <v>9552</v>
+        <v>16742</v>
+      </c>
+      <c r="M145">
+        <v>15318</v>
       </c>
       <c r="N145">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R145">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="S145">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T145">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B146">
         <v>41</v>
       </c>
       <c r="C146">
+        <v>221</v>
+      </c>
+      <c r="D146">
+        <v>20101</v>
+      </c>
+      <c r="E146">
+        <v>23595</v>
+      </c>
+      <c r="G146">
+        <v>18294</v>
+      </c>
+      <c r="H146">
+        <v>16676</v>
+      </c>
+      <c r="I146">
+        <v>18198</v>
+      </c>
+      <c r="J146">
+        <v>22408</v>
+      </c>
+      <c r="K146">
+        <v>20414</v>
+      </c>
+      <c r="L146">
+        <v>15462</v>
+      </c>
+      <c r="M146">
+        <v>23397</v>
+      </c>
+      <c r="N146">
+        <v>-4</v>
+      </c>
+      <c r="O146">
+        <v>6</v>
+      </c>
+      <c r="P146">
+        <v>-1</v>
+      </c>
+      <c r="Q146">
+        <v>-3</v>
+      </c>
+      <c r="R146">
+        <v>-4</v>
+      </c>
+      <c r="S146">
+        <v>6</v>
+      </c>
+      <c r="T146">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>908</v>
+      </c>
+      <c r="B147">
+        <v>41</v>
+      </c>
+      <c r="C147">
+        <v>5</v>
+      </c>
+      <c r="D147">
+        <v>20110</v>
+      </c>
+      <c r="E147">
+        <v>23939</v>
+      </c>
+      <c r="F147">
+        <v>16880</v>
+      </c>
+      <c r="H147">
+        <v>18401</v>
+      </c>
+      <c r="I147">
+        <v>24215</v>
+      </c>
+      <c r="J147">
+        <v>10543</v>
+      </c>
+      <c r="K147">
+        <v>19639</v>
+      </c>
+      <c r="M147">
+        <v>22159</v>
+      </c>
+      <c r="N147">
+        <v>-6</v>
+      </c>
+      <c r="O147">
+        <v>2</v>
+      </c>
+      <c r="P147">
+        <v>5</v>
+      </c>
+      <c r="Q147">
+        <v>1</v>
+      </c>
+      <c r="R147">
+        <v>3</v>
+      </c>
+      <c r="S147">
+        <v>-8</v>
+      </c>
+      <c r="T147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>909</v>
+      </c>
+      <c r="B148">
+        <v>221</v>
+      </c>
+      <c r="C148">
+        <v>5</v>
+      </c>
+      <c r="D148">
+        <v>16876</v>
+      </c>
+      <c r="E148">
+        <v>19236</v>
+      </c>
+      <c r="F148">
+        <v>17028</v>
+      </c>
+      <c r="G148">
+        <v>19078</v>
+      </c>
+      <c r="H148">
+        <v>18003</v>
+      </c>
+      <c r="I148">
+        <v>17132</v>
+      </c>
+      <c r="J148">
+        <v>17763</v>
+      </c>
+      <c r="L148">
+        <v>12862</v>
+      </c>
+      <c r="N148">
+        <v>5</v>
+      </c>
+      <c r="O148">
+        <v>-10</v>
+      </c>
+      <c r="P148">
+        <v>-3</v>
+      </c>
+      <c r="Q148">
+        <v>0</v>
+      </c>
+      <c r="R148">
+        <v>5</v>
+      </c>
+      <c r="S148">
+        <v>-6</v>
+      </c>
+      <c r="T148">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>910</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+      <c r="C149">
+        <v>311</v>
+      </c>
+      <c r="E149">
+        <v>24157</v>
+      </c>
+      <c r="F149">
+        <v>20352</v>
+      </c>
+      <c r="G149">
+        <v>18263</v>
+      </c>
+      <c r="H149">
+        <v>23818</v>
+      </c>
+      <c r="I149">
+        <v>26648</v>
+      </c>
+      <c r="J149">
+        <v>18253</v>
+      </c>
+      <c r="K149">
+        <v>25292</v>
+      </c>
+      <c r="L149">
+        <v>23025</v>
+      </c>
+      <c r="M149">
+        <v>23030</v>
+      </c>
+      <c r="N149">
+        <v>-5</v>
+      </c>
+      <c r="O149">
+        <v>6</v>
+      </c>
+      <c r="P149">
+        <v>5</v>
+      </c>
+      <c r="Q149">
+        <v>-9</v>
+      </c>
+      <c r="R149">
+        <v>-2</v>
+      </c>
+      <c r="S149">
+        <v>-2</v>
+      </c>
+      <c r="T149">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>912</v>
+      </c>
+      <c r="B150">
+        <v>221</v>
+      </c>
+      <c r="C150">
+        <v>5</v>
+      </c>
+      <c r="D150">
+        <v>18357</v>
+      </c>
+      <c r="E150">
+        <v>14502</v>
+      </c>
+      <c r="F150">
+        <v>18557</v>
+      </c>
+      <c r="G150">
+        <v>13574</v>
+      </c>
+      <c r="I150">
+        <v>10586</v>
+      </c>
+      <c r="J150">
+        <v>9581</v>
+      </c>
+      <c r="L150">
+        <v>22723</v>
+      </c>
+      <c r="M150">
+        <v>10388</v>
+      </c>
+      <c r="N150">
+        <v>4</v>
+      </c>
+      <c r="O150">
+        <v>1</v>
+      </c>
+      <c r="P150">
+        <v>-1</v>
+      </c>
+      <c r="Q150">
+        <v>2</v>
+      </c>
+      <c r="R150">
+        <v>1</v>
+      </c>
+      <c r="S150">
+        <v>-3</v>
+      </c>
+      <c r="T150">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>913</v>
+      </c>
+      <c r="B151">
+        <v>221</v>
+      </c>
+      <c r="C151">
         <v>2111</v>
       </c>
-      <c r="D146">
-        <v>17921</v>
-      </c>
-      <c r="E146">
-        <v>16416</v>
-      </c>
-      <c r="F146">
+      <c r="D151">
+        <v>17879</v>
+      </c>
+      <c r="E151">
+        <v>14400</v>
+      </c>
+      <c r="F151">
+        <v>15123</v>
+      </c>
+      <c r="G151">
+        <v>15760</v>
+      </c>
+      <c r="H151">
+        <v>14892</v>
+      </c>
+      <c r="I151">
+        <v>17225</v>
+      </c>
+      <c r="J151">
+        <v>15824</v>
+      </c>
+      <c r="K151">
+        <v>10890</v>
+      </c>
+      <c r="L151">
+        <v>19999</v>
+      </c>
+      <c r="M151">
+        <v>15356</v>
+      </c>
+      <c r="N151">
+        <v>-6</v>
+      </c>
+      <c r="O151">
+        <v>4</v>
+      </c>
+      <c r="P151">
+        <v>4</v>
+      </c>
+      <c r="Q151">
+        <v>5</v>
+      </c>
+      <c r="R151">
+        <v>2</v>
+      </c>
+      <c r="S151">
+        <v>-6</v>
+      </c>
+      <c r="T151">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>914</v>
+      </c>
+      <c r="B152">
+        <v>221</v>
+      </c>
+      <c r="C152">
+        <v>5</v>
+      </c>
+      <c r="D152">
+        <v>21628</v>
+      </c>
+      <c r="E152">
+        <v>14574</v>
+      </c>
+      <c r="F152">
+        <v>18248</v>
+      </c>
+      <c r="G152">
+        <v>14042</v>
+      </c>
+      <c r="H152">
+        <v>21079</v>
+      </c>
+      <c r="I152">
+        <v>20443</v>
+      </c>
+      <c r="J152">
+        <v>19603</v>
+      </c>
+      <c r="K152">
+        <v>22705</v>
+      </c>
+      <c r="L152">
+        <v>16711</v>
+      </c>
+      <c r="M152">
+        <v>8266</v>
+      </c>
+      <c r="N152">
+        <v>-8</v>
+      </c>
+      <c r="O152">
+        <v>-1</v>
+      </c>
+      <c r="P152">
+        <v>3</v>
+      </c>
+      <c r="Q152">
+        <v>-7</v>
+      </c>
+      <c r="R152">
+        <v>-4</v>
+      </c>
+      <c r="S152">
+        <v>12</v>
+      </c>
+      <c r="T152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>915</v>
+      </c>
+      <c r="B153">
+        <v>2111</v>
+      </c>
+      <c r="C153">
+        <v>311</v>
+      </c>
+      <c r="D153">
+        <v>18722</v>
+      </c>
+      <c r="E153">
+        <v>17922</v>
+      </c>
+      <c r="F153">
+        <v>16318</v>
+      </c>
+      <c r="G153">
+        <v>19192</v>
+      </c>
+      <c r="H153">
+        <v>17856</v>
+      </c>
+      <c r="I153">
+        <v>19348</v>
+      </c>
+      <c r="J153">
+        <v>18925</v>
+      </c>
+      <c r="K153">
+        <v>15726</v>
+      </c>
+      <c r="L153">
+        <v>22301</v>
+      </c>
+      <c r="M153">
+        <v>15000</v>
+      </c>
+      <c r="N153">
+        <v>-2</v>
+      </c>
+      <c r="O153">
+        <v>8</v>
+      </c>
+      <c r="P153">
+        <v>1</v>
+      </c>
+      <c r="Q153">
+        <v>-10</v>
+      </c>
+      <c r="R153">
+        <v>-1</v>
+      </c>
+      <c r="S153">
+        <v>2</v>
+      </c>
+      <c r="T153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>916</v>
+      </c>
+      <c r="B154">
+        <v>221</v>
+      </c>
+      <c r="C154">
+        <v>2111</v>
+      </c>
+      <c r="D154">
+        <v>14898</v>
+      </c>
+      <c r="E154">
+        <v>8609</v>
+      </c>
+      <c r="F154">
+        <v>12480</v>
+      </c>
+      <c r="J154">
+        <v>13035</v>
+      </c>
+      <c r="K154">
+        <v>11335</v>
+      </c>
+      <c r="L154">
+        <v>13685</v>
+      </c>
+      <c r="N154">
+        <v>-2</v>
+      </c>
+      <c r="O154">
+        <v>11</v>
+      </c>
+      <c r="P154">
+        <v>1</v>
+      </c>
+      <c r="Q154">
+        <v>2</v>
+      </c>
+      <c r="R154">
+        <v>3</v>
+      </c>
+      <c r="S154">
+        <v>-1</v>
+      </c>
+      <c r="T154">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>917</v>
+      </c>
+      <c r="B155">
+        <v>32</v>
+      </c>
+      <c r="C155">
+        <v>2111</v>
+      </c>
+      <c r="D155">
         <v>14999</v>
       </c>
-      <c r="G146">
-        <v>14452</v>
-      </c>
-      <c r="H146">
-        <v>16725</v>
-      </c>
-      <c r="I146">
-        <v>16979</v>
-      </c>
-      <c r="J146">
-        <v>16561</v>
-      </c>
-      <c r="L146">
+      <c r="E155">
+        <v>9114</v>
+      </c>
+      <c r="G155">
+        <v>10626</v>
+      </c>
+      <c r="I155">
+        <v>14516</v>
+      </c>
+      <c r="J155">
+        <v>14547</v>
+      </c>
+      <c r="K155">
+        <v>13335</v>
+      </c>
+      <c r="L155">
+        <v>13559</v>
+      </c>
+      <c r="N155">
+        <v>3</v>
+      </c>
+      <c r="O155">
+        <v>-7</v>
+      </c>
+      <c r="P155">
+        <v>-1</v>
+      </c>
+      <c r="Q155">
+        <v>-5</v>
+      </c>
+      <c r="R155">
+        <v>-1</v>
+      </c>
+      <c r="S155">
+        <v>-3</v>
+      </c>
+      <c r="T155">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>918</v>
+      </c>
+      <c r="B156">
+        <v>221</v>
+      </c>
+      <c r="C156">
+        <v>41</v>
+      </c>
+      <c r="D156">
+        <v>9012</v>
+      </c>
+      <c r="E156">
+        <v>14898</v>
+      </c>
+      <c r="F156">
+        <v>12563</v>
+      </c>
+      <c r="G156">
+        <v>11968</v>
+      </c>
+      <c r="I156">
+        <v>17112</v>
+      </c>
+      <c r="J156">
+        <v>7628</v>
+      </c>
+      <c r="K156">
+        <v>7791</v>
+      </c>
+      <c r="L156">
+        <v>16485</v>
+      </c>
+      <c r="M156">
+        <v>12170</v>
+      </c>
+      <c r="N156">
+        <v>-1</v>
+      </c>
+      <c r="O156">
+        <v>3</v>
+      </c>
+      <c r="P156">
+        <v>-7</v>
+      </c>
+      <c r="Q156">
+        <v>6</v>
+      </c>
+      <c r="R156">
+        <v>4</v>
+      </c>
+      <c r="S156">
+        <v>-3</v>
+      </c>
+      <c r="T156">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>919</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+      <c r="C157">
+        <v>2111</v>
+      </c>
+      <c r="D157">
+        <v>24400</v>
+      </c>
+      <c r="E157">
+        <v>14999</v>
+      </c>
+      <c r="F157">
+        <v>18214</v>
+      </c>
+      <c r="H157">
+        <v>20500</v>
+      </c>
+      <c r="I157">
+        <v>20532</v>
+      </c>
+      <c r="J157">
+        <v>20104</v>
+      </c>
+      <c r="K157">
+        <v>21507</v>
+      </c>
+      <c r="L157">
+        <v>15434</v>
+      </c>
+      <c r="M157">
+        <v>18890</v>
+      </c>
+      <c r="N157">
+        <v>-1</v>
+      </c>
+      <c r="O157">
+        <v>1</v>
+      </c>
+      <c r="P157">
+        <v>2</v>
+      </c>
+      <c r="Q157">
+        <v>-5</v>
+      </c>
+      <c r="R157">
+        <v>3</v>
+      </c>
+      <c r="S157">
+        <v>-1</v>
+      </c>
+      <c r="T157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>920</v>
+      </c>
+      <c r="B158">
+        <v>41</v>
+      </c>
+      <c r="C158">
+        <v>311</v>
+      </c>
+      <c r="D158">
+        <v>20772</v>
+      </c>
+      <c r="E158">
+        <v>24007</v>
+      </c>
+      <c r="F158">
+        <v>14884</v>
+      </c>
+      <c r="G158">
+        <v>17869</v>
+      </c>
+      <c r="H158">
+        <v>20121</v>
+      </c>
+      <c r="I158">
+        <v>20398</v>
+      </c>
+      <c r="J158">
+        <v>20373</v>
+      </c>
+      <c r="K158">
+        <v>21038</v>
+      </c>
+      <c r="L158">
+        <v>15517</v>
+      </c>
+      <c r="M158">
+        <v>21002</v>
+      </c>
+      <c r="N158">
+        <v>-10</v>
+      </c>
+      <c r="O158">
+        <v>1</v>
+      </c>
+      <c r="P158">
+        <v>2</v>
+      </c>
+      <c r="Q158">
+        <v>3</v>
+      </c>
+      <c r="R158">
+        <v>3</v>
+      </c>
+      <c r="S158">
+        <v>-4</v>
+      </c>
+      <c r="T158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>922</v>
+      </c>
+      <c r="B159">
+        <v>2111</v>
+      </c>
+      <c r="C159">
+        <v>221</v>
+      </c>
+      <c r="D159">
+        <v>17858</v>
+      </c>
+      <c r="E159">
+        <v>17603</v>
+      </c>
+      <c r="F159">
+        <v>14506</v>
+      </c>
+      <c r="G159">
+        <v>19333</v>
+      </c>
+      <c r="H159">
+        <v>15365</v>
+      </c>
+      <c r="I159">
+        <v>19724</v>
+      </c>
+      <c r="J159">
+        <v>17838</v>
+      </c>
+      <c r="K159">
+        <v>16926</v>
+      </c>
+      <c r="N159">
+        <v>5</v>
+      </c>
+      <c r="O159">
+        <v>3</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+      <c r="Q159">
+        <v>4</v>
+      </c>
+      <c r="R159">
+        <v>9</v>
+      </c>
+      <c r="S159">
+        <v>0</v>
+      </c>
+      <c r="T159">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>923</v>
+      </c>
+      <c r="B160">
+        <v>311</v>
+      </c>
+      <c r="C160">
+        <v>5</v>
+      </c>
+      <c r="D160">
+        <v>17575</v>
+      </c>
+      <c r="E160">
+        <v>14808</v>
+      </c>
+      <c r="F160">
+        <v>15882</v>
+      </c>
+      <c r="G160">
+        <v>17712</v>
+      </c>
+      <c r="H160">
+        <v>15838</v>
+      </c>
+      <c r="I160">
+        <v>17000</v>
+      </c>
+      <c r="J160">
+        <v>14508</v>
+      </c>
+      <c r="K160">
+        <v>12908</v>
+      </c>
+      <c r="L160">
+        <v>17969</v>
+      </c>
+      <c r="M160">
+        <v>11776</v>
+      </c>
+      <c r="N160">
+        <v>-2</v>
+      </c>
+      <c r="O160">
+        <v>8</v>
+      </c>
+      <c r="P160">
+        <v>-5</v>
+      </c>
+      <c r="Q160">
+        <v>0</v>
+      </c>
+      <c r="R160">
+        <v>5</v>
+      </c>
+      <c r="S160">
+        <v>-2</v>
+      </c>
+      <c r="T160">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>924</v>
+      </c>
+      <c r="B161">
+        <v>2111</v>
+      </c>
+      <c r="C161">
+        <v>2111</v>
+      </c>
+      <c r="D161">
+        <v>17121</v>
+      </c>
+      <c r="E161">
+        <v>16403</v>
+      </c>
+      <c r="F161">
+        <v>17232</v>
+      </c>
+      <c r="G161">
+        <v>16331</v>
+      </c>
+      <c r="H161">
+        <v>16330</v>
+      </c>
+      <c r="I161">
+        <v>16972</v>
+      </c>
+      <c r="K161">
+        <v>16552</v>
+      </c>
+      <c r="L161">
+        <v>19667</v>
+      </c>
+      <c r="M161">
+        <v>12055</v>
+      </c>
+      <c r="N161">
+        <v>2</v>
+      </c>
+      <c r="O161">
+        <v>-4</v>
+      </c>
+      <c r="P161">
+        <v>3</v>
+      </c>
+      <c r="Q161">
+        <v>4</v>
+      </c>
+      <c r="R161">
+        <v>1</v>
+      </c>
+      <c r="S161">
+        <v>0</v>
+      </c>
+      <c r="T161">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>925</v>
+      </c>
+      <c r="B162">
+        <v>311</v>
+      </c>
+      <c r="C162">
+        <v>221</v>
+      </c>
+      <c r="D162">
+        <v>21219</v>
+      </c>
+      <c r="E162">
+        <v>19885</v>
+      </c>
+      <c r="F162">
+        <v>24483</v>
+      </c>
+      <c r="G162">
+        <v>16471</v>
+      </c>
+      <c r="H162">
         <v>16742</v>
       </c>
-      <c r="M146">
-        <v>15318</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>5</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
+      <c r="I162">
+        <v>23145</v>
+      </c>
+      <c r="J162">
+        <v>18392</v>
+      </c>
+      <c r="K162">
+        <v>19999</v>
+      </c>
+      <c r="L162">
+        <v>22416</v>
+      </c>
+      <c r="N162">
+        <v>-9</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>-1</v>
+      </c>
+      <c r="R162">
+        <v>8</v>
+      </c>
+      <c r="S162">
+        <v>6</v>
+      </c>
+      <c r="T162">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>926</v>
+      </c>
+      <c r="B163">
+        <v>41</v>
+      </c>
+      <c r="C163">
+        <v>5</v>
+      </c>
+      <c r="D163">
+        <v>24834</v>
+      </c>
+      <c r="E163">
+        <v>16782</v>
+      </c>
+      <c r="F163">
+        <v>17111</v>
+      </c>
+      <c r="G163">
+        <v>15935</v>
+      </c>
+      <c r="H163">
+        <v>18309</v>
+      </c>
+      <c r="I163">
+        <v>18600</v>
+      </c>
+      <c r="K163">
+        <v>16580</v>
+      </c>
+      <c r="M163">
+        <v>25122</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163">
+        <v>8</v>
+      </c>
+      <c r="P163">
+        <v>-1</v>
+      </c>
+      <c r="Q163">
+        <v>8</v>
+      </c>
+      <c r="R163">
+        <v>0</v>
+      </c>
+      <c r="S163">
+        <v>0</v>
+      </c>
+      <c r="T163">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>927</v>
+      </c>
+      <c r="B164">
+        <v>5</v>
+      </c>
+      <c r="C164">
+        <v>221</v>
+      </c>
+      <c r="D164">
+        <v>13880</v>
+      </c>
+      <c r="E164">
+        <v>9663</v>
+      </c>
+      <c r="G164">
+        <v>6665</v>
+      </c>
+      <c r="H164">
+        <v>17353</v>
+      </c>
+      <c r="I164">
+        <v>12578</v>
+      </c>
+      <c r="K164">
+        <v>9548</v>
+      </c>
+      <c r="L164">
+        <v>12253</v>
+      </c>
+      <c r="M164">
+        <v>11585</v>
+      </c>
+      <c r="N164">
+        <v>-2</v>
+      </c>
+      <c r="O164">
+        <v>-8</v>
+      </c>
+      <c r="P164">
+        <v>3</v>
+      </c>
+      <c r="Q164">
+        <v>-3</v>
+      </c>
+      <c r="R164">
+        <v>2</v>
+      </c>
+      <c r="S164">
+        <v>-2</v>
+      </c>
+      <c r="T164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>928</v>
+      </c>
+      <c r="B165">
+        <v>311</v>
+      </c>
+      <c r="C165">
+        <v>5</v>
+      </c>
+      <c r="D165">
+        <v>17083</v>
+      </c>
+      <c r="E165">
+        <v>17266</v>
+      </c>
+      <c r="F165">
+        <v>20100</v>
+      </c>
+      <c r="G165">
+        <v>12452</v>
+      </c>
+      <c r="H165">
+        <v>16383</v>
+      </c>
+      <c r="I165">
+        <v>10394</v>
+      </c>
+      <c r="J165">
+        <v>13990</v>
+      </c>
+      <c r="K165">
+        <v>21894</v>
+      </c>
+      <c r="L165">
+        <v>15117</v>
+      </c>
+      <c r="M165">
+        <v>10818</v>
+      </c>
+      <c r="N165">
+        <v>-5</v>
+      </c>
+      <c r="O165">
+        <v>-2</v>
+      </c>
+      <c r="P165">
+        <v>-1</v>
+      </c>
+      <c r="Q165">
+        <v>-2</v>
+      </c>
+      <c r="R165">
+        <v>1</v>
+      </c>
+      <c r="S165">
         <v>4</v>
       </c>
-      <c r="R146">
+      <c r="T165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>929</v>
+      </c>
+      <c r="B166">
+        <v>2111</v>
+      </c>
+      <c r="C166">
+        <v>11111</v>
+      </c>
+      <c r="D166">
+        <v>18160</v>
+      </c>
+      <c r="E166">
+        <v>17768</v>
+      </c>
+      <c r="F166">
+        <v>18859</v>
+      </c>
+      <c r="G166">
+        <v>16394</v>
+      </c>
+      <c r="H166">
+        <v>16622</v>
+      </c>
+      <c r="I166">
+        <v>18025</v>
+      </c>
+      <c r="J166">
+        <v>17872</v>
+      </c>
+      <c r="K166">
+        <v>16536</v>
+      </c>
+      <c r="L166">
+        <v>17192</v>
+      </c>
+      <c r="M166">
+        <v>16531</v>
+      </c>
+      <c r="N166">
+        <v>-6</v>
+      </c>
+      <c r="O166">
+        <v>9</v>
+      </c>
+      <c r="P166">
+        <v>3</v>
+      </c>
+      <c r="Q166">
         <v>-5</v>
       </c>
-      <c r="S146">
+      <c r="R166">
+        <v>0</v>
+      </c>
+      <c r="S166">
+        <v>0</v>
+      </c>
+      <c r="T166">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>930</v>
+      </c>
+      <c r="B167">
+        <v>11111</v>
+      </c>
+      <c r="C167">
+        <v>11111</v>
+      </c>
+      <c r="E167">
+        <v>17719</v>
+      </c>
+      <c r="F167">
+        <v>16933</v>
+      </c>
+      <c r="H167">
+        <v>16595</v>
+      </c>
+      <c r="I167">
+        <v>18222</v>
+      </c>
+      <c r="K167">
+        <v>17369</v>
+      </c>
+      <c r="M167">
+        <v>16705</v>
+      </c>
+      <c r="N167">
+        <v>-4</v>
+      </c>
+      <c r="O167">
+        <v>2</v>
+      </c>
+      <c r="P167">
+        <v>-1</v>
+      </c>
+      <c r="Q167">
+        <v>-4</v>
+      </c>
+      <c r="R167">
         <v>7</v>
       </c>
-      <c r="T146">
+      <c r="S167">
+        <v>-4</v>
+      </c>
+      <c r="T167">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>931</v>
+      </c>
+      <c r="B168">
+        <v>311</v>
+      </c>
+      <c r="C168">
+        <v>5</v>
+      </c>
+      <c r="D168">
+        <v>23357</v>
+      </c>
+      <c r="E168"/>
+      <c r="F168">
+        <v>25563</v>
+      </c>
+      <c r="G168">
+        <v>16585</v>
+      </c>
+      <c r="H168">
+        <v>24351</v>
+      </c>
+      <c r="I168">
+        <v>24999</v>
+      </c>
+      <c r="J168">
+        <v>20339</v>
+      </c>
+      <c r="K168">
+        <v>23914</v>
+      </c>
+      <c r="L168">
+        <v>16812</v>
+      </c>
+      <c r="M168">
+        <v>22428</v>
+      </c>
+      <c r="N168">
         <v>-3</v>
+      </c>
+      <c r="O168">
+        <v>6</v>
+      </c>
+      <c r="P168">
+        <v>3</v>
+      </c>
+      <c r="Q168">
+        <v>-1</v>
+      </c>
+      <c r="R168">
+        <v>0</v>
+      </c>
+      <c r="S168">
+        <v>-8</v>
+      </c>
+      <c r="T168">
+        <v>3</v>
+      </c>
+      <c r="U168"/>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>932</v>
+      </c>
+      <c r="B169">
+        <v>5</v>
+      </c>
+      <c r="C169">
+        <v>311</v>
+      </c>
+      <c r="D169">
+        <v>24671</v>
+      </c>
+      <c r="E169">
+        <v>16886</v>
+      </c>
+      <c r="F169">
+        <v>25870</v>
+      </c>
+      <c r="G169">
+        <v>20555</v>
+      </c>
+      <c r="H169">
+        <v>17042</v>
+      </c>
+      <c r="I169">
+        <v>21056</v>
+      </c>
+      <c r="J169">
+        <v>20953</v>
+      </c>
+      <c r="K169">
+        <v>19330</v>
+      </c>
+      <c r="L169">
+        <v>22579</v>
+      </c>
+      <c r="M169">
+        <v>16545</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>-6</v>
+      </c>
+      <c r="P169">
+        <v>3</v>
+      </c>
+      <c r="Q169">
+        <v>5</v>
+      </c>
+      <c r="R169">
+        <v>-1</v>
+      </c>
+      <c r="S169">
+        <v>1</v>
+      </c>
+      <c r="T169">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>933</v>
+      </c>
+      <c r="B170">
+        <v>5</v>
+      </c>
+      <c r="C170">
+        <v>32</v>
+      </c>
+      <c r="D170">
+        <v>24975</v>
+      </c>
+      <c r="E170">
+        <v>17198</v>
+      </c>
+      <c r="F170">
+        <v>20864</v>
+      </c>
+      <c r="G170">
+        <v>17413</v>
+      </c>
+      <c r="H170">
+        <v>15968</v>
+      </c>
+      <c r="I170">
+        <v>20877</v>
+      </c>
+      <c r="J170">
+        <v>23878</v>
+      </c>
+      <c r="K170">
+        <v>21477</v>
+      </c>
+      <c r="L170">
+        <v>22155</v>
+      </c>
+      <c r="M170">
+        <v>18255</v>
+      </c>
+      <c r="N170">
+        <v>-10</v>
+      </c>
+      <c r="O170">
+        <v>19</v>
+      </c>
+      <c r="P170">
+        <v>1</v>
+      </c>
+      <c r="Q170">
+        <v>-5</v>
+      </c>
+      <c r="R170">
+        <v>-6</v>
+      </c>
+      <c r="S170">
+        <v>0</v>
+      </c>
+      <c r="T170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>934</v>
+      </c>
+      <c r="B171">
+        <v>5</v>
+      </c>
+      <c r="C171">
+        <v>11111</v>
+      </c>
+      <c r="D171">
+        <v>24999</v>
+      </c>
+      <c r="E171">
+        <v>17566</v>
+      </c>
+      <c r="F171">
+        <v>21222</v>
+      </c>
+      <c r="G171">
+        <v>17790</v>
+      </c>
+      <c r="H171">
+        <v>26254</v>
+      </c>
+      <c r="I171">
+        <v>23079</v>
+      </c>
+      <c r="J171">
+        <v>22614</v>
+      </c>
+      <c r="K171">
+        <v>22400</v>
+      </c>
+      <c r="L171">
+        <v>22375</v>
+      </c>
+      <c r="M171">
+        <v>21682</v>
+      </c>
+      <c r="N171">
+        <v>-9</v>
+      </c>
+      <c r="O171">
+        <v>10</v>
+      </c>
+      <c r="P171">
+        <v>-2</v>
+      </c>
+      <c r="Q171">
+        <v>4</v>
+      </c>
+      <c r="R171">
+        <v>-3</v>
+      </c>
+      <c r="S171">
+        <v>2</v>
+      </c>
+      <c r="T171">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>935</v>
+      </c>
+      <c r="B172">
+        <v>221</v>
+      </c>
+      <c r="C172">
+        <v>2111</v>
+      </c>
+      <c r="D172">
+        <v>9508</v>
+      </c>
+      <c r="E172">
+        <v>11512</v>
+      </c>
+      <c r="F172">
+        <v>9428</v>
+      </c>
+      <c r="I172">
+        <v>10100</v>
+      </c>
+      <c r="J172">
+        <v>10114</v>
+      </c>
+      <c r="L172">
+        <v>10459</v>
+      </c>
+      <c r="M172">
+        <v>9784</v>
+      </c>
+      <c r="N172">
+        <v>8</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>3</v>
+      </c>
+      <c r="Q172">
+        <v>0</v>
+      </c>
+      <c r="R172">
+        <v>-5</v>
+      </c>
+      <c r="S172">
+        <v>1</v>
+      </c>
+      <c r="T172">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>936</v>
+      </c>
+      <c r="B173">
+        <v>2111</v>
+      </c>
+      <c r="C173">
+        <v>32</v>
+      </c>
+      <c r="D173">
+        <v>18177</v>
+      </c>
+      <c r="E173">
+        <v>17923</v>
+      </c>
+      <c r="F173">
+        <v>17958</v>
+      </c>
+      <c r="G173">
+        <v>14316</v>
+      </c>
+      <c r="H173">
+        <v>19799</v>
+      </c>
+      <c r="I173">
+        <v>20223</v>
+      </c>
+      <c r="K173">
+        <v>19949</v>
+      </c>
+      <c r="L173">
+        <v>18416</v>
+      </c>
+      <c r="M173">
+        <v>15982</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173">
+        <v>2</v>
+      </c>
+      <c r="P173">
+        <v>1</v>
+      </c>
+      <c r="Q173">
+        <v>-5</v>
+      </c>
+      <c r="R173">
+        <v>2</v>
+      </c>
+      <c r="S173">
+        <v>5</v>
+      </c>
+      <c r="T173">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>937</v>
+      </c>
+      <c r="B174">
+        <v>5</v>
+      </c>
+      <c r="C174">
+        <v>41</v>
+      </c>
+      <c r="D174">
+        <v>3246</v>
+      </c>
+      <c r="E174">
+        <v>9303</v>
+      </c>
+      <c r="F174">
+        <v>6850</v>
+      </c>
+      <c r="G174">
+        <v>3089</v>
+      </c>
+      <c r="H174">
+        <v>9386</v>
+      </c>
+      <c r="I174">
+        <v>6762</v>
+      </c>
+      <c r="J174">
+        <v>3144</v>
+      </c>
+      <c r="K174">
+        <v>9999</v>
+      </c>
+      <c r="L174">
+        <v>7550</v>
+      </c>
+      <c r="M174">
+        <v>7199</v>
+      </c>
+      <c r="N174">
+        <v>-4</v>
+      </c>
+      <c r="O174">
+        <v>3</v>
+      </c>
+      <c r="P174">
+        <v>1</v>
+      </c>
+      <c r="Q174">
+        <v>3</v>
+      </c>
+      <c r="R174">
+        <v>5</v>
+      </c>
+      <c r="S174">
+        <v>-2</v>
+      </c>
+      <c r="T174">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>938</v>
+      </c>
+      <c r="B175">
+        <v>5</v>
+      </c>
+      <c r="C175">
+        <v>311</v>
+      </c>
+      <c r="D175">
+        <v>3134</v>
+      </c>
+      <c r="E175">
+        <v>8976</v>
+      </c>
+      <c r="F175">
+        <v>3917</v>
+      </c>
+      <c r="G175">
+        <v>9262</v>
+      </c>
+      <c r="H175">
+        <v>2980</v>
+      </c>
+      <c r="I175">
+        <v>6351</v>
+      </c>
+      <c r="J175">
+        <v>7547</v>
+      </c>
+      <c r="K175">
+        <v>5112</v>
+      </c>
+      <c r="L175">
+        <v>6146</v>
+      </c>
+      <c r="M175">
+        <v>4888</v>
+      </c>
+      <c r="N175">
+        <v>5</v>
+      </c>
+      <c r="O175">
+        <v>-5</v>
+      </c>
+      <c r="P175">
+        <v>2</v>
+      </c>
+      <c r="Q175">
+        <v>-11</v>
+      </c>
+      <c r="R175">
+        <v>5</v>
+      </c>
+      <c r="S175">
+        <v>6</v>
+      </c>
+      <c r="T175">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>939</v>
+      </c>
+      <c r="B176">
+        <v>5</v>
+      </c>
+      <c r="C176">
+        <v>311</v>
+      </c>
+      <c r="D176">
+        <v>3194</v>
+      </c>
+      <c r="E176">
+        <v>3032</v>
+      </c>
+      <c r="F176">
+        <v>3973</v>
+      </c>
+      <c r="G176">
+        <v>9324</v>
+      </c>
+      <c r="H176">
+        <v>2208</v>
+      </c>
+      <c r="I176">
+        <v>3058</v>
+      </c>
+      <c r="J176">
+        <v>8005</v>
+      </c>
+      <c r="L176">
+        <v>4660</v>
+      </c>
+      <c r="M176">
+        <v>4155</v>
+      </c>
+      <c r="N176">
+        <v>6</v>
+      </c>
+      <c r="O176">
+        <v>-1</v>
+      </c>
+      <c r="P176">
+        <v>-2</v>
+      </c>
+      <c r="Q176">
+        <v>-4</v>
+      </c>
+      <c r="R176">
+        <v>5</v>
+      </c>
+      <c r="S176">
+        <v>3</v>
+      </c>
+      <c r="T176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>941</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+      <c r="C177">
+        <v>311</v>
+      </c>
+      <c r="D177">
+        <v>1989</v>
+      </c>
+      <c r="E177">
+        <v>3709</v>
+      </c>
+      <c r="F177">
+        <v>8988</v>
+      </c>
+      <c r="G177">
+        <v>2963</v>
+      </c>
+      <c r="H177">
+        <v>2791</v>
+      </c>
+      <c r="I177">
+        <v>5021</v>
+      </c>
+      <c r="J177">
+        <v>4539</v>
+      </c>
+      <c r="K177">
+        <v>4162</v>
+      </c>
+      <c r="L177">
+        <v>5191</v>
+      </c>
+      <c r="M177">
+        <v>3552</v>
+      </c>
+      <c r="N177">
+        <v>3</v>
+      </c>
+      <c r="O177">
+        <v>-8</v>
+      </c>
+      <c r="P177">
+        <v>0</v>
+      </c>
+      <c r="Q177">
+        <v>1</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+      <c r="S177">
+        <v>4</v>
+      </c>
+      <c r="T177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>942</v>
+      </c>
+      <c r="B178">
+        <v>41</v>
+      </c>
+      <c r="C178">
+        <v>11111</v>
+      </c>
+      <c r="D178">
+        <v>1869</v>
+      </c>
+      <c r="E178">
+        <v>3591</v>
+      </c>
+      <c r="F178">
+        <v>8739</v>
+      </c>
+      <c r="G178">
+        <v>2849</v>
+      </c>
+      <c r="H178">
+        <v>3745</v>
+      </c>
+      <c r="I178">
+        <v>4163</v>
+      </c>
+      <c r="J178">
+        <v>4104</v>
+      </c>
+      <c r="K178">
+        <v>4016</v>
+      </c>
+      <c r="L178">
+        <v>3952</v>
+      </c>
+      <c r="M178">
+        <v>3831</v>
+      </c>
+      <c r="N178">
+        <v>-2</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+      <c r="Q178">
+        <v>0</v>
+      </c>
+      <c r="R178">
+        <v>2</v>
+      </c>
+      <c r="S178">
+        <v>2</v>
+      </c>
+      <c r="T178">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>943</v>
+      </c>
+      <c r="B179">
+        <v>221</v>
+      </c>
+      <c r="C179">
+        <v>41</v>
+      </c>
+      <c r="D179">
+        <v>7017</v>
+      </c>
+      <c r="E179">
+        <v>5801</v>
+      </c>
+      <c r="F179">
+        <v>3049</v>
+      </c>
+      <c r="G179">
+        <v>9119</v>
+      </c>
+      <c r="H179">
+        <v>5217</v>
+      </c>
+      <c r="I179">
+        <v>5615</v>
+      </c>
+      <c r="J179">
+        <v>1591</v>
+      </c>
+      <c r="K179">
+        <v>10116</v>
+      </c>
+      <c r="L179">
+        <v>1234</v>
+      </c>
+      <c r="M179">
+        <v>3469</v>
+      </c>
+      <c r="N179">
+        <v>-2</v>
+      </c>
+      <c r="O179">
+        <v>-1</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+      <c r="Q179">
+        <v>-3</v>
+      </c>
+      <c r="R179">
+        <v>6</v>
+      </c>
+      <c r="S179">
+        <v>0</v>
+      </c>
+      <c r="T179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>944</v>
+      </c>
+      <c r="B180">
+        <v>41</v>
+      </c>
+      <c r="C180">
+        <v>2111</v>
+      </c>
+      <c r="D180">
+        <v>5416</v>
+      </c>
+      <c r="E180">
+        <v>3173</v>
+      </c>
+      <c r="F180">
+        <v>9489</v>
+      </c>
+      <c r="G180">
+        <v>2679</v>
+      </c>
+      <c r="H180">
+        <v>6533</v>
+      </c>
+      <c r="I180">
+        <v>3903</v>
+      </c>
+      <c r="J180">
+        <v>7039</v>
+      </c>
+      <c r="K180">
+        <v>5259</v>
+      </c>
+      <c r="L180">
+        <v>5065</v>
+      </c>
+      <c r="N180">
+        <v>5</v>
+      </c>
+      <c r="O180">
+        <v>-9</v>
+      </c>
+      <c r="P180">
+        <v>0</v>
+      </c>
+      <c r="Q180">
+        <v>5</v>
+      </c>
+      <c r="R180">
+        <v>3</v>
+      </c>
+      <c r="S180">
+        <v>4</v>
+      </c>
+      <c r="T180">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>945</v>
+      </c>
+      <c r="B181">
+        <v>5</v>
+      </c>
+      <c r="C181">
+        <v>221</v>
+      </c>
+      <c r="D181">
+        <v>3274</v>
+      </c>
+      <c r="E181">
+        <v>9843</v>
+      </c>
+      <c r="F181">
+        <v>2912</v>
+      </c>
+      <c r="G181">
+        <v>6896</v>
+      </c>
+      <c r="H181">
+        <v>3812</v>
+      </c>
+      <c r="I181">
+        <v>9731</v>
+      </c>
+      <c r="J181">
+        <v>2601</v>
+      </c>
+      <c r="K181">
+        <v>4999</v>
+      </c>
+      <c r="L181">
+        <v>1000</v>
+      </c>
+      <c r="M181">
+        <v>9584</v>
+      </c>
+      <c r="N181">
+        <v>12</v>
+      </c>
+      <c r="O181">
+        <v>-7</v>
+      </c>
+      <c r="P181">
+        <v>2</v>
+      </c>
+      <c r="Q181">
+        <v>-5</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+      <c r="S181">
+        <v>2</v>
+      </c>
+      <c r="T181">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>946</v>
+      </c>
+      <c r="B182">
+        <v>5</v>
+      </c>
+      <c r="C182">
+        <v>32</v>
+      </c>
+      <c r="D182">
+        <v>3094</v>
+      </c>
+      <c r="E182">
+        <v>9573</v>
+      </c>
+      <c r="F182">
+        <v>2752</v>
+      </c>
+      <c r="G182">
+        <v>6538</v>
+      </c>
+      <c r="H182">
+        <v>3673</v>
+      </c>
+      <c r="I182">
+        <v>7873</v>
+      </c>
+      <c r="J182">
+        <v>4888</v>
+      </c>
+      <c r="K182">
+        <v>3375</v>
+      </c>
+      <c r="L182">
+        <v>5444</v>
+      </c>
+      <c r="M182">
+        <v>4649</v>
+      </c>
+      <c r="N182">
+        <v>6</v>
+      </c>
+      <c r="O182">
+        <v>-8</v>
+      </c>
+      <c r="P182">
+        <v>1</v>
+      </c>
+      <c r="Q182">
+        <v>-2</v>
+      </c>
+      <c r="R182">
+        <v>4</v>
+      </c>
+      <c r="S182">
+        <v>2</v>
+      </c>
+      <c r="T182">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>947</v>
+      </c>
+      <c r="B183">
+        <v>5</v>
+      </c>
+      <c r="C183">
+        <v>2111</v>
+      </c>
+      <c r="F183">
+        <v>18282</v>
+      </c>
+      <c r="H183">
+        <v>19999</v>
+      </c>
+      <c r="I183">
+        <v>22013</v>
+      </c>
+      <c r="J183">
+        <v>20656</v>
+      </c>
+      <c r="K183">
+        <v>19128</v>
+      </c>
+      <c r="L183">
+        <v>21699</v>
+      </c>
+      <c r="M183">
+        <v>17111</v>
+      </c>
+      <c r="N183">
+        <v>-5</v>
+      </c>
+      <c r="O183">
+        <v>12</v>
+      </c>
+      <c r="P183">
+        <v>-2</v>
+      </c>
+      <c r="Q183">
+        <v>-4</v>
+      </c>
+      <c r="R183">
+        <v>6</v>
+      </c>
+      <c r="S183">
+        <v>-5</v>
+      </c>
+      <c r="T183">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>948</v>
+      </c>
+      <c r="B184">
+        <v>2111</v>
+      </c>
+      <c r="C184">
+        <v>5</v>
+      </c>
+      <c r="D184">
+        <v>14999</v>
+      </c>
+      <c r="E184">
+        <v>21619</v>
+      </c>
+      <c r="F184">
+        <v>18651</v>
+      </c>
+      <c r="G184">
+        <v>18209</v>
+      </c>
+      <c r="H184">
+        <v>18340</v>
+      </c>
+      <c r="I184">
+        <v>21882</v>
+      </c>
+      <c r="J184">
+        <v>14565</v>
+      </c>
+      <c r="K184">
+        <v>20118</v>
+      </c>
+      <c r="L184">
+        <v>14381</v>
+      </c>
+      <c r="M184">
+        <v>14999</v>
+      </c>
+      <c r="N184">
+        <v>6</v>
+      </c>
+      <c r="O184">
+        <v>10</v>
+      </c>
+      <c r="P184">
+        <v>-2</v>
+      </c>
+      <c r="Q184">
+        <v>-3</v>
+      </c>
+      <c r="R184">
+        <v>-7</v>
+      </c>
+      <c r="S184">
+        <v>2</v>
+      </c>
+      <c r="T184">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>949</v>
+      </c>
+      <c r="B185">
+        <v>11111</v>
+      </c>
+      <c r="C185">
+        <v>5</v>
+      </c>
+      <c r="E185">
+        <v>18446</v>
+      </c>
+      <c r="F185">
+        <v>18388</v>
+      </c>
+      <c r="G185">
+        <v>18248</v>
+      </c>
+      <c r="H185">
+        <v>17535</v>
+      </c>
+      <c r="J185">
+        <v>12609</v>
+      </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
+      <c r="O185">
+        <v>7</v>
+      </c>
+      <c r="P185">
+        <v>3</v>
+      </c>
+      <c r="Q185">
+        <v>8</v>
+      </c>
+      <c r="R185">
+        <v>5</v>
+      </c>
+      <c r="S185">
+        <v>4</v>
+      </c>
+      <c r="T185">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>950</v>
+      </c>
+      <c r="B186">
+        <v>11111</v>
+      </c>
+      <c r="C186">
+        <v>11111</v>
+      </c>
+      <c r="D186">
+        <v>18602</v>
+      </c>
+      <c r="E186">
+        <v>18476</v>
+      </c>
+      <c r="F186">
+        <v>18164</v>
+      </c>
+      <c r="H186">
+        <v>17914</v>
+      </c>
+      <c r="I186">
+        <v>18756</v>
+      </c>
+      <c r="J186">
+        <v>17340</v>
+      </c>
+      <c r="L186">
+        <v>18086</v>
+      </c>
+      <c r="M186">
+        <v>18073</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>11</v>
+      </c>
+      <c r="P186">
+        <v>-1</v>
+      </c>
+      <c r="Q186">
+        <v>2</v>
+      </c>
+      <c r="R186">
+        <v>-3</v>
+      </c>
+      <c r="S186">
+        <v>3</v>
+      </c>
+      <c r="T186">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>951</v>
+      </c>
+      <c r="B187">
+        <v>2111</v>
+      </c>
+      <c r="C187">
+        <v>311</v>
+      </c>
+      <c r="D187">
+        <v>19484</v>
+      </c>
+      <c r="E187">
+        <v>19999</v>
+      </c>
+      <c r="F187">
+        <v>17615</v>
+      </c>
+      <c r="G187">
+        <v>18967</v>
+      </c>
+      <c r="H187">
+        <v>17222</v>
+      </c>
+      <c r="I187">
+        <v>19236</v>
+      </c>
+      <c r="J187">
+        <v>19124</v>
+      </c>
+      <c r="K187">
+        <v>23622</v>
+      </c>
+      <c r="L187">
+        <v>14236</v>
+      </c>
+      <c r="M187">
+        <v>14349</v>
+      </c>
+      <c r="N187">
+        <v>-4</v>
+      </c>
+      <c r="O187">
+        <v>-10</v>
+      </c>
+      <c r="P187">
+        <v>3</v>
+      </c>
+      <c r="Q187">
+        <v>6</v>
+      </c>
+      <c r="R187">
+        <v>4</v>
+      </c>
+      <c r="S187">
+        <v>2</v>
+      </c>
+      <c r="T187">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>952</v>
+      </c>
+      <c r="B188">
+        <v>2111</v>
+      </c>
+      <c r="C188">
+        <v>5</v>
+      </c>
+      <c r="D188">
+        <v>19507</v>
+      </c>
+      <c r="E188">
+        <v>19346</v>
+      </c>
+      <c r="F188">
+        <v>18552</v>
+      </c>
+      <c r="G188">
+        <v>20120</v>
+      </c>
+      <c r="H188">
+        <v>19313</v>
+      </c>
+      <c r="I188">
+        <v>17534</v>
+      </c>
+      <c r="J188">
+        <v>17859</v>
+      </c>
+      <c r="K188">
+        <v>17602</v>
+      </c>
+      <c r="L188">
+        <v>15917</v>
+      </c>
+      <c r="M188">
+        <v>20716</v>
+      </c>
+      <c r="N188">
+        <v>3</v>
+      </c>
+      <c r="O188">
+        <v>-9</v>
+      </c>
+      <c r="P188">
+        <v>-1</v>
+      </c>
+      <c r="Q188">
+        <v>6</v>
+      </c>
+      <c r="R188">
+        <v>3</v>
+      </c>
+      <c r="S188">
+        <v>4</v>
+      </c>
+      <c r="T188">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>953</v>
+      </c>
+      <c r="B189">
+        <v>11111</v>
+      </c>
+      <c r="C189">
+        <v>221</v>
+      </c>
+      <c r="D189">
+        <v>22057</v>
+      </c>
+      <c r="E189">
+        <v>20544</v>
+      </c>
+      <c r="F189">
+        <v>20381</v>
+      </c>
+      <c r="G189">
+        <v>19554</v>
+      </c>
+      <c r="H189">
+        <v>19546</v>
+      </c>
+      <c r="I189">
+        <v>21976</v>
+      </c>
+      <c r="J189">
+        <v>18704</v>
+      </c>
+      <c r="K189">
+        <v>19999</v>
+      </c>
+      <c r="L189">
+        <v>19888</v>
+      </c>
+      <c r="M189">
+        <v>20460</v>
+      </c>
+      <c r="N189">
+        <v>-2</v>
+      </c>
+      <c r="O189">
+        <v>-1</v>
+      </c>
+      <c r="P189">
+        <v>0</v>
+      </c>
+      <c r="Q189">
+        <v>-5</v>
+      </c>
+      <c r="R189">
+        <v>6</v>
+      </c>
+      <c r="S189">
+        <v>1</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>954</v>
+      </c>
+      <c r="B190">
+        <v>11111</v>
+      </c>
+      <c r="C190">
+        <v>41</v>
+      </c>
+      <c r="D190">
+        <v>19577</v>
+      </c>
+      <c r="E190">
+        <v>19185</v>
+      </c>
+      <c r="G190">
+        <v>18978</v>
+      </c>
+      <c r="H190">
+        <v>18910</v>
+      </c>
+      <c r="I190">
+        <v>20947</v>
+      </c>
+      <c r="J190">
+        <v>20112</v>
+      </c>
+      <c r="K190">
+        <v>16640</v>
+      </c>
+      <c r="L190">
+        <v>18691</v>
+      </c>
+      <c r="M190">
+        <v>18667</v>
+      </c>
+      <c r="N190">
+        <v>-7</v>
+      </c>
+      <c r="O190">
+        <v>-7</v>
+      </c>
+      <c r="P190">
+        <v>-2</v>
+      </c>
+      <c r="Q190">
+        <v>-3</v>
+      </c>
+      <c r="R190">
+        <v>5</v>
+      </c>
+      <c r="S190">
+        <v>5</v>
+      </c>
+      <c r="T190">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>955</v>
+      </c>
+      <c r="B191">
+        <v>311</v>
+      </c>
+      <c r="C191">
+        <v>2111</v>
+      </c>
+      <c r="D191">
+        <v>20942</v>
+      </c>
+      <c r="E191">
+        <v>19527</v>
+      </c>
+      <c r="F191">
+        <v>20752</v>
+      </c>
+      <c r="G191">
+        <v>17262</v>
+      </c>
+      <c r="H191">
+        <v>19131</v>
+      </c>
+      <c r="I191">
+        <v>20630</v>
+      </c>
+      <c r="J191">
+        <v>18458</v>
+      </c>
+      <c r="K191">
+        <v>20926</v>
+      </c>
+      <c r="L191">
+        <v>19316</v>
+      </c>
+      <c r="M191">
+        <v>18616</v>
+      </c>
+      <c r="N191">
+        <v>8</v>
+      </c>
+      <c r="O191">
+        <v>-3</v>
+      </c>
+      <c r="P191">
+        <v>5</v>
+      </c>
+      <c r="Q191">
+        <v>-4</v>
+      </c>
+      <c r="R191">
+        <v>-2</v>
+      </c>
+      <c r="S191">
+        <v>-3</v>
+      </c>
+      <c r="T191">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>956</v>
+      </c>
+      <c r="B192">
+        <v>2111</v>
+      </c>
+      <c r="C192">
+        <v>311</v>
+      </c>
+      <c r="D192">
+        <v>20266</v>
+      </c>
+      <c r="E192">
+        <v>18871</v>
+      </c>
+      <c r="F192">
+        <v>21177</v>
+      </c>
+      <c r="G192">
+        <v>19576</v>
+      </c>
+      <c r="H192">
+        <v>19201</v>
+      </c>
+      <c r="I192">
+        <v>20316</v>
+      </c>
+      <c r="J192">
+        <v>19895</v>
+      </c>
+      <c r="K192">
+        <v>18749</v>
+      </c>
+      <c r="L192">
+        <v>20625</v>
+      </c>
+      <c r="M192">
+        <v>19888</v>
+      </c>
+      <c r="N192">
+        <v>4</v>
+      </c>
+      <c r="O192">
+        <v>3</v>
+      </c>
+      <c r="P192">
+        <v>3</v>
+      </c>
+      <c r="Q192">
+        <v>0</v>
+      </c>
+      <c r="R192">
+        <v>-1</v>
+      </c>
+      <c r="S192">
+        <v>-6</v>
+      </c>
+      <c r="T192">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>957</v>
+      </c>
+      <c r="B193">
+        <v>11111</v>
+      </c>
+      <c r="C193">
+        <v>221</v>
+      </c>
+      <c r="D193">
+        <v>19761</v>
+      </c>
+      <c r="E193">
+        <v>19653</v>
+      </c>
+      <c r="F193">
+        <v>19405</v>
+      </c>
+      <c r="G193">
+        <v>19288</v>
+      </c>
+      <c r="H193">
+        <v>19252</v>
+      </c>
+      <c r="I193">
+        <v>21516</v>
+      </c>
+      <c r="J193">
+        <v>22398</v>
+      </c>
+      <c r="K193">
+        <v>15705</v>
+      </c>
+      <c r="L193">
+        <v>19940</v>
+      </c>
+      <c r="M193">
+        <v>17709</v>
+      </c>
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193">
+        <v>5</v>
+      </c>
+      <c r="P193">
+        <v>2</v>
+      </c>
+      <c r="Q193">
+        <v>-2</v>
+      </c>
+      <c r="R193">
+        <v>6</v>
+      </c>
+      <c r="S193">
+        <v>-6</v>
+      </c>
+      <c r="T193">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>958</v>
+      </c>
+      <c r="B194">
+        <v>11111</v>
+      </c>
+      <c r="C194">
+        <v>221</v>
+      </c>
+      <c r="D194">
+        <v>19646</v>
+      </c>
+      <c r="E194">
+        <v>19735</v>
+      </c>
+      <c r="G194">
+        <v>19000</v>
+      </c>
+      <c r="H194">
+        <v>18835</v>
+      </c>
+      <c r="I194">
+        <v>22210</v>
+      </c>
+      <c r="J194">
+        <v>17874</v>
+      </c>
+      <c r="K194">
+        <v>19473</v>
+      </c>
+      <c r="L194">
+        <v>18566</v>
+      </c>
+      <c r="M194">
+        <v>18745</v>
+      </c>
+      <c r="N194">
+        <v>-6</v>
+      </c>
+      <c r="O194">
+        <v>2</v>
+      </c>
+      <c r="P194">
+        <v>5</v>
+      </c>
+      <c r="Q194">
+        <v>-3</v>
+      </c>
+      <c r="R194">
+        <v>3</v>
+      </c>
+      <c r="S194">
+        <v>-1</v>
+      </c>
+      <c r="T194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>959</v>
+      </c>
+      <c r="B195">
+        <v>2111</v>
+      </c>
+      <c r="C195">
+        <v>11111</v>
+      </c>
+      <c r="D195">
+        <v>19674</v>
+      </c>
+      <c r="F195">
+        <v>16777</v>
+      </c>
+      <c r="G195">
+        <v>21162</v>
+      </c>
+      <c r="H195">
+        <v>18501</v>
+      </c>
+      <c r="I195">
+        <v>20060</v>
+      </c>
+      <c r="J195">
+        <v>19477</v>
+      </c>
+      <c r="K195">
+        <v>18781</v>
+      </c>
+      <c r="L195">
+        <v>19261</v>
+      </c>
+      <c r="N195">
+        <v>-2</v>
+      </c>
+      <c r="O195">
+        <v>2</v>
+      </c>
+      <c r="P195">
+        <v>0</v>
+      </c>
+      <c r="Q195">
+        <v>-1</v>
+      </c>
+      <c r="R195">
+        <v>-1</v>
+      </c>
+      <c r="S195">
+        <v>0</v>
+      </c>
+      <c r="T195">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>960</v>
+      </c>
+      <c r="B196">
+        <v>11111</v>
+      </c>
+      <c r="C196">
+        <v>221</v>
+      </c>
+      <c r="D196">
+        <v>18706</v>
+      </c>
+      <c r="E196">
+        <v>18145</v>
+      </c>
+      <c r="F196">
+        <v>17794</v>
+      </c>
+      <c r="G196">
+        <v>17248</v>
+      </c>
+      <c r="H196">
+        <v>16798</v>
+      </c>
+      <c r="K196">
+        <v>17409</v>
+      </c>
+      <c r="L196">
+        <v>18074</v>
+      </c>
+      <c r="M196">
+        <v>15851</v>
+      </c>
+      <c r="N196">
+        <v>-1</v>
+      </c>
+      <c r="O196">
+        <v>4</v>
+      </c>
+      <c r="P196">
+        <v>3</v>
+      </c>
+      <c r="Q196">
+        <v>5</v>
+      </c>
+      <c r="R196">
+        <v>5</v>
+      </c>
+      <c r="S196">
+        <v>-3</v>
+      </c>
+      <c r="T196">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>961</v>
+      </c>
+      <c r="B197">
+        <v>2111</v>
+      </c>
+      <c r="C197">
+        <v>32</v>
+      </c>
+      <c r="D197">
+        <v>18416</v>
+      </c>
+      <c r="E197">
+        <v>18240</v>
+      </c>
+      <c r="F197">
+        <v>17798</v>
+      </c>
+      <c r="G197">
+        <v>17518</v>
+      </c>
+      <c r="I197">
+        <v>21296</v>
+      </c>
+      <c r="J197">
+        <v>15836</v>
+      </c>
+      <c r="L197">
+        <v>13013</v>
+      </c>
+      <c r="M197">
+        <v>18810</v>
+      </c>
+      <c r="N197">
+        <v>-6</v>
+      </c>
+      <c r="O197">
+        <v>-3</v>
+      </c>
+      <c r="P197">
+        <v>6</v>
+      </c>
+      <c r="Q197">
+        <v>2</v>
+      </c>
+      <c r="R197">
+        <v>10</v>
+      </c>
+      <c r="S197">
+        <v>-1</v>
+      </c>
+      <c r="T197">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>962</v>
+      </c>
+      <c r="B198">
+        <v>221</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+      <c r="D198">
+        <v>15122</v>
+      </c>
+      <c r="E198">
+        <v>20109</v>
+      </c>
+      <c r="F198">
+        <v>17317</v>
+      </c>
+      <c r="G198">
+        <v>17435</v>
+      </c>
+      <c r="H198">
+        <v>17331</v>
+      </c>
+      <c r="I198">
+        <v>7563</v>
+      </c>
+      <c r="J198">
+        <v>15000</v>
+      </c>
+      <c r="K198">
+        <v>21047</v>
+      </c>
+      <c r="L198">
+        <v>14888</v>
+      </c>
+      <c r="M198">
+        <v>20361</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <v>-1</v>
+      </c>
+      <c r="P198">
+        <v>1</v>
+      </c>
+      <c r="Q198">
+        <v>-5</v>
+      </c>
+      <c r="R198">
+        <v>2</v>
+      </c>
+      <c r="S198">
+        <v>2</v>
+      </c>
+      <c r="T198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>963</v>
+      </c>
+      <c r="B199">
+        <v>221</v>
+      </c>
+      <c r="C199">
+        <v>5</v>
+      </c>
+      <c r="D199">
+        <v>18914</v>
+      </c>
+      <c r="E199">
+        <v>19728</v>
+      </c>
+      <c r="F199">
+        <v>16645</v>
+      </c>
+      <c r="G199">
+        <v>17583</v>
+      </c>
+      <c r="I199">
+        <v>21670</v>
+      </c>
+      <c r="J199">
+        <v>8572</v>
+      </c>
+      <c r="L199">
+        <v>14074</v>
+      </c>
+      <c r="N199">
+        <v>9</v>
+      </c>
+      <c r="O199">
+        <v>-6</v>
+      </c>
+      <c r="P199">
+        <v>-7</v>
+      </c>
+      <c r="Q199">
+        <v>4</v>
+      </c>
+      <c r="R199">
+        <v>4</v>
+      </c>
+      <c r="S199">
+        <v>3</v>
+      </c>
+      <c r="T199">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>964</v>
+      </c>
+      <c r="B200">
+        <v>221</v>
+      </c>
+      <c r="C200">
+        <v>41</v>
+      </c>
+      <c r="D200">
+        <v>18993</v>
+      </c>
+      <c r="E200">
+        <v>16763</v>
+      </c>
+      <c r="F200">
+        <v>18388</v>
+      </c>
+      <c r="G200">
+        <v>16298</v>
+      </c>
+      <c r="H200">
+        <v>17845</v>
+      </c>
+      <c r="I200">
+        <v>17850</v>
+      </c>
+      <c r="J200">
+        <v>14409</v>
+      </c>
+      <c r="K200">
+        <v>19891</v>
+      </c>
+      <c r="L200">
+        <v>15533</v>
+      </c>
+      <c r="M200">
+        <v>17364</v>
+      </c>
+      <c r="N200">
+        <v>-10</v>
+      </c>
+      <c r="O200">
+        <v>10</v>
+      </c>
+      <c r="P200">
+        <v>1</v>
+      </c>
+      <c r="Q200">
+        <v>7</v>
+      </c>
+      <c r="R200">
+        <v>6</v>
+      </c>
+      <c r="S200">
+        <v>-9</v>
+      </c>
+      <c r="T200">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>966</v>
+      </c>
+      <c r="B201">
+        <v>311</v>
+      </c>
+      <c r="C201">
+        <v>32</v>
+      </c>
+      <c r="E201">
+        <v>18445</v>
+      </c>
+      <c r="F201">
+        <v>17136</v>
+      </c>
+      <c r="G201">
+        <v>17825</v>
+      </c>
+      <c r="H201">
+        <v>17659</v>
+      </c>
+      <c r="I201">
+        <v>19989</v>
+      </c>
+      <c r="J201">
+        <v>17134</v>
+      </c>
+      <c r="K201">
+        <v>15513</v>
+      </c>
+      <c r="L201">
+        <v>14257</v>
+      </c>
+      <c r="M201">
+        <v>20159</v>
+      </c>
+      <c r="N201">
+        <v>-10</v>
+      </c>
+      <c r="O201">
+        <v>7</v>
+      </c>
+      <c r="P201">
+        <v>-1</v>
+      </c>
+      <c r="Q201">
+        <v>5</v>
+      </c>
+      <c r="R201">
+        <v>2</v>
+      </c>
+      <c r="S201">
+        <v>-3</v>
+      </c>
+      <c r="T201">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>967</v>
+      </c>
+      <c r="B202">
+        <v>5</v>
+      </c>
+      <c r="C202">
+        <v>311</v>
+      </c>
+      <c r="D202">
+        <v>26406</v>
+      </c>
+      <c r="E202">
+        <v>26890</v>
+      </c>
+      <c r="F202">
+        <v>16775</v>
+      </c>
+      <c r="H202">
+        <v>18181</v>
+      </c>
+      <c r="I202">
+        <v>21932</v>
+      </c>
+      <c r="J202">
+        <v>21822</v>
+      </c>
+      <c r="L202">
+        <v>17572</v>
+      </c>
+      <c r="N202">
+        <v>-7</v>
+      </c>
+      <c r="O202">
+        <v>3</v>
+      </c>
+      <c r="P202">
+        <v>3</v>
+      </c>
+      <c r="Q202">
+        <v>9</v>
+      </c>
+      <c r="R202">
+        <v>-6</v>
+      </c>
+      <c r="S202">
+        <v>5</v>
+      </c>
+      <c r="T202">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>976</v>
+      </c>
+      <c r="B212">
+        <v>221</v>
+      </c>
+      <c r="C212">
+        <v>5</v>
+      </c>
+      <c r="H212">
+        <v>15554</v>
+      </c>
+      <c r="L212">
+        <v>3878</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212">
+        <v>-9</v>
+      </c>
+      <c r="Q212">
+        <v>-3</v>
+      </c>
+      <c r="R212">
+        <v>-11</v>
+      </c>
+      <c r="S212">
+        <v>1</v>
+      </c>
+      <c r="T212">
+        <v>3</v>
+      </c>
+      <c r="U212">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>977</v>
+      </c>
+      <c r="B213">
+        <v>5</v>
+      </c>
+      <c r="C213">
+        <v>32</v>
+      </c>
+      <c r="E213">
+        <v>6512</v>
+      </c>
+      <c r="N213">
+        <v>-3</v>
+      </c>
+      <c r="O213">
+        <v>-1</v>
+      </c>
+      <c r="Q213">
+        <v>-1</v>
+      </c>
+      <c r="R213">
+        <v>3</v>
+      </c>
+      <c r="S213">
+        <v>3</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>978</v>
+      </c>
+      <c r="B214">
+        <v>5</v>
+      </c>
+      <c r="C214">
+        <v>5</v>
+      </c>
+      <c r="E214">
+        <v>6935</v>
+      </c>
+      <c r="L214">
+        <v>4548</v>
+      </c>
+      <c r="M214">
+        <v>13023</v>
+      </c>
+      <c r="N214">
+        <v>-11</v>
+      </c>
+      <c r="O214">
+        <v>-8</v>
+      </c>
+      <c r="Q214">
+        <v>-1</v>
+      </c>
+      <c r="R214">
+        <v>1</v>
+      </c>
+      <c r="S214">
+        <v>-6</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>990</v>
+      </c>
+      <c r="B229">
+        <v>11111</v>
+      </c>
+      <c r="C229">
+        <v>2111</v>
+      </c>
+      <c r="D229">
+        <v>18392</v>
+      </c>
+      <c r="F229">
+        <v>18139</v>
+      </c>
+      <c r="G229">
+        <v>17868</v>
+      </c>
+      <c r="H229">
+        <v>17709</v>
+      </c>
+      <c r="K229">
+        <v>18119</v>
+      </c>
+      <c r="M229">
+        <v>17250</v>
+      </c>
+      <c r="N229">
+        <v>3</v>
+      </c>
+      <c r="O229">
+        <v>10</v>
+      </c>
+      <c r="Q229">
+        <v>0</v>
+      </c>
+      <c r="R229">
+        <v>4</v>
+      </c>
+      <c r="S229">
+        <v>4</v>
+      </c>
+      <c r="T229">
+        <v>3</v>
+      </c>
+      <c r="U229">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>992</v>
+      </c>
+      <c r="B230">
+        <v>311</v>
+      </c>
+      <c r="C230">
+        <v>221</v>
+      </c>
+      <c r="D230">
+        <v>18380</v>
+      </c>
+      <c r="G230">
+        <v>14981</v>
+      </c>
+      <c r="I230">
+        <v>17842</v>
+      </c>
+      <c r="J230">
+        <v>18630</v>
+      </c>
+      <c r="L230">
+        <v>15117</v>
+      </c>
+      <c r="M230">
+        <v>18260</v>
+      </c>
+      <c r="N230">
+        <v>-3</v>
+      </c>
+      <c r="O230">
+        <v>-1</v>
+      </c>
+      <c r="Q230">
+        <v>-5</v>
+      </c>
+      <c r="R230">
+        <v>2</v>
+      </c>
+      <c r="S230">
+        <v>1</v>
+      </c>
+      <c r="T230">
+        <v>-4</v>
+      </c>
+      <c r="U230">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>999</v>
+      </c>
+      <c r="B237">
+        <v>5</v>
+      </c>
+      <c r="C237">
+        <v>311</v>
+      </c>
+      <c r="D237">
+        <v>4898</v>
+      </c>
+      <c r="E237">
+        <v>3527</v>
+      </c>
+      <c r="G237">
+        <v>4553</v>
+      </c>
+      <c r="I237">
+        <v>6885</v>
+      </c>
+      <c r="J237">
+        <v>6872</v>
+      </c>
+      <c r="K237">
+        <v>8932</v>
+      </c>
+      <c r="M237">
+        <v>9114</v>
+      </c>
+      <c r="N237">
+        <v>-5</v>
+      </c>
+      <c r="O237">
+        <v>1</v>
+      </c>
+      <c r="Q237">
+        <v>-10</v>
+      </c>
+      <c r="R237">
+        <v>7</v>
+      </c>
+      <c r="S237">
+        <v>3</v>
+      </c>
+      <c r="T237">
+        <v>-1</v>
+      </c>
+      <c r="U237">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>1000</v>
+      </c>
+      <c r="B238">
+        <v>5</v>
+      </c>
+      <c r="C238">
+        <v>41</v>
+      </c>
+      <c r="D238">
+        <v>3580</v>
+      </c>
+      <c r="E238">
+        <v>4952</v>
+      </c>
+      <c r="I238">
+        <v>3372</v>
+      </c>
+      <c r="K238">
+        <v>5467</v>
+      </c>
+      <c r="N238">
+        <v>-3</v>
+      </c>
+      <c r="O238">
+        <v>5</v>
+      </c>
+      <c r="Q238">
+        <v>0</v>
+      </c>
+      <c r="R238">
+        <v>4</v>
+      </c>
+      <c r="S238">
+        <v>2</v>
+      </c>
+      <c r="T238">
+        <v>-6</v>
+      </c>
+      <c r="U238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>1001</v>
+      </c>
+      <c r="B239">
+        <v>5</v>
+      </c>
+      <c r="C239">
+        <v>2111</v>
+      </c>
+      <c r="D239">
+        <v>3704</v>
+      </c>
+      <c r="H239">
+        <v>12528</v>
+      </c>
+      <c r="J239">
+        <v>6609</v>
+      </c>
+      <c r="K239">
+        <v>8845</v>
+      </c>
+      <c r="L239">
+        <v>8091</v>
+      </c>
+      <c r="M239">
+        <v>7545</v>
+      </c>
+      <c r="N239">
+        <v>-4</v>
+      </c>
+      <c r="O239">
+        <v>-5</v>
+      </c>
+      <c r="Q239">
+        <v>-9</v>
+      </c>
+      <c r="R239">
+        <v>10</v>
+      </c>
+      <c r="S239">
+        <v>-1</v>
+      </c>
+      <c r="T239">
+        <v>-1</v>
+      </c>
+      <c r="U239">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/xlsx/CSPreMatchStatistics.xlsx
+++ b/datasets/xlsx/CSPreMatchStatistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08758215-5FB8-411D-8C9A-DAF79B6E70FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D60CA6-D09C-4EBE-9BF5-2A19937B8350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U239"/>
+  <dimension ref="A1:U237"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -12202,364 +12202,786 @@
         <v>-7</v>
       </c>
     </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>968</v>
+      </c>
+      <c r="B203">
+        <v>5</v>
+      </c>
+      <c r="C203">
+        <v>311</v>
+      </c>
+      <c r="D203">
+        <v>26678</v>
+      </c>
+      <c r="E203">
+        <v>17126</v>
+      </c>
+      <c r="F203">
+        <v>27153</v>
+      </c>
+      <c r="G203">
+        <v>15536</v>
+      </c>
+      <c r="H203">
+        <v>18536</v>
+      </c>
+      <c r="I203">
+        <v>22585</v>
+      </c>
+      <c r="J203">
+        <v>22566</v>
+      </c>
+      <c r="K203">
+        <v>22829</v>
+      </c>
+      <c r="L203">
+        <v>21035</v>
+      </c>
+      <c r="M203">
+        <v>22124</v>
+      </c>
+      <c r="N203">
+        <v>-2</v>
+      </c>
+      <c r="O203">
+        <v>6</v>
+      </c>
+      <c r="P203">
+        <v>3</v>
+      </c>
+      <c r="Q203">
+        <v>3</v>
+      </c>
+      <c r="R203">
+        <v>-4</v>
+      </c>
+      <c r="S203">
+        <v>2</v>
+      </c>
+      <c r="T203">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>969</v>
+      </c>
+      <c r="B204">
+        <v>5</v>
+      </c>
+      <c r="C204">
+        <v>41</v>
+      </c>
+      <c r="D204">
+        <v>26443</v>
+      </c>
+      <c r="E204">
+        <v>16859</v>
+      </c>
+      <c r="F204">
+        <v>26923</v>
+      </c>
+      <c r="G204">
+        <v>18279</v>
+      </c>
+      <c r="H204">
+        <v>15424</v>
+      </c>
+      <c r="I204">
+        <v>23451</v>
+      </c>
+      <c r="J204">
+        <v>18756</v>
+      </c>
+      <c r="K204">
+        <v>16770</v>
+      </c>
+      <c r="L204">
+        <v>25246</v>
+      </c>
+      <c r="M204">
+        <v>23485</v>
+      </c>
+      <c r="N204">
+        <v>-11</v>
+      </c>
+      <c r="O204">
+        <v>2</v>
+      </c>
+      <c r="P204">
+        <v>9</v>
+      </c>
+      <c r="Q204">
+        <v>-4</v>
+      </c>
+      <c r="R204">
+        <v>-2</v>
+      </c>
+      <c r="S204">
+        <v>5</v>
+      </c>
+      <c r="T204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>970</v>
+      </c>
+      <c r="B205">
+        <v>5</v>
+      </c>
+      <c r="C205">
+        <v>2111</v>
+      </c>
+      <c r="D205">
+        <v>18631</v>
+      </c>
+      <c r="E205">
+        <v>17229</v>
+      </c>
+      <c r="F205">
+        <v>27215</v>
+      </c>
+      <c r="H205">
+        <v>26869</v>
+      </c>
+      <c r="I205">
+        <v>22118</v>
+      </c>
+      <c r="J205">
+        <v>22834</v>
+      </c>
+      <c r="K205">
+        <v>23610</v>
+      </c>
+      <c r="L205">
+        <v>23183</v>
+      </c>
+      <c r="M205">
+        <v>22783</v>
+      </c>
+      <c r="N205">
+        <v>-9</v>
+      </c>
+      <c r="O205">
+        <v>2</v>
+      </c>
+      <c r="P205">
+        <v>5</v>
+      </c>
+      <c r="Q205">
+        <v>4</v>
+      </c>
+      <c r="R205">
+        <v>-1</v>
+      </c>
+      <c r="S205">
+        <v>6</v>
+      </c>
+      <c r="T205">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>971</v>
+      </c>
+      <c r="B206">
+        <v>41</v>
+      </c>
+      <c r="C206">
+        <v>2111</v>
+      </c>
+      <c r="D206">
+        <v>21040</v>
+      </c>
+      <c r="E206">
+        <v>18292</v>
+      </c>
+      <c r="F206">
+        <v>16889</v>
+      </c>
+      <c r="H206">
+        <v>17719</v>
+      </c>
+      <c r="I206">
+        <v>21150</v>
+      </c>
+      <c r="J206">
+        <v>19405</v>
+      </c>
+      <c r="K206">
+        <v>22094</v>
+      </c>
+      <c r="L206">
+        <v>18381</v>
+      </c>
+      <c r="M206">
+        <v>20482</v>
+      </c>
+      <c r="N206">
+        <v>-4</v>
+      </c>
+      <c r="O206">
+        <v>6</v>
+      </c>
+      <c r="P206">
+        <v>1</v>
+      </c>
+      <c r="Q206">
+        <v>-4</v>
+      </c>
+      <c r="R206">
+        <v>5</v>
+      </c>
+      <c r="S206">
+        <v>-1</v>
+      </c>
+      <c r="T206">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>972</v>
+      </c>
+      <c r="B207">
+        <v>5</v>
+      </c>
+      <c r="C207">
+        <v>221</v>
+      </c>
+      <c r="D207">
+        <v>18073</v>
+      </c>
+      <c r="E207">
+        <v>16662</v>
+      </c>
+      <c r="G207">
+        <v>16071</v>
+      </c>
+      <c r="H207">
+        <v>17500</v>
+      </c>
+      <c r="I207">
+        <v>16392</v>
+      </c>
+      <c r="J207">
+        <v>23172</v>
+      </c>
+      <c r="K207">
+        <v>20000</v>
+      </c>
+      <c r="L207">
+        <v>18631</v>
+      </c>
+      <c r="M207">
+        <v>20000</v>
+      </c>
+      <c r="N207">
+        <v>-3</v>
+      </c>
+      <c r="O207">
+        <v>9</v>
+      </c>
+      <c r="P207">
+        <v>5</v>
+      </c>
+      <c r="Q207">
+        <v>-7</v>
+      </c>
+      <c r="R207">
+        <v>2</v>
+      </c>
+      <c r="S207">
+        <v>-3</v>
+      </c>
+      <c r="T207">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>974</v>
+      </c>
+      <c r="B208">
+        <v>221</v>
+      </c>
+      <c r="C208">
+        <v>311</v>
+      </c>
+      <c r="D208">
+        <v>17731</v>
+      </c>
+      <c r="E208">
+        <v>17914</v>
+      </c>
+      <c r="F208">
+        <v>17578</v>
+      </c>
+      <c r="G208">
+        <v>18441</v>
+      </c>
+      <c r="H208">
+        <v>15348</v>
+      </c>
+      <c r="I208">
+        <v>17850</v>
+      </c>
+      <c r="J208">
+        <v>17706</v>
+      </c>
+      <c r="K208">
+        <v>17161</v>
+      </c>
+      <c r="L208">
+        <v>10556</v>
+      </c>
+      <c r="M208">
+        <v>19999</v>
+      </c>
+      <c r="N208">
+        <v>-3</v>
+      </c>
+      <c r="O208">
+        <v>-9</v>
+      </c>
+      <c r="P208">
+        <v>4</v>
+      </c>
+      <c r="Q208">
+        <v>-2</v>
+      </c>
+      <c r="R208">
+        <v>11</v>
+      </c>
+      <c r="S208">
+        <v>4</v>
+      </c>
+      <c r="T208">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>975</v>
+      </c>
+      <c r="B209">
+        <v>32</v>
+      </c>
+      <c r="C209">
+        <v>311</v>
+      </c>
+      <c r="D209">
+        <v>18709</v>
+      </c>
+      <c r="E209">
+        <v>13611</v>
+      </c>
+      <c r="F209">
+        <v>18569</v>
+      </c>
+      <c r="G209">
+        <v>18152</v>
+      </c>
+      <c r="H209">
+        <v>15000</v>
+      </c>
+      <c r="I209">
+        <v>16711</v>
+      </c>
+      <c r="J209">
+        <v>17007</v>
+      </c>
+      <c r="K209">
+        <v>15107</v>
+      </c>
+      <c r="L209">
+        <v>12976</v>
+      </c>
+      <c r="N209">
+        <v>-1</v>
+      </c>
+      <c r="O209">
+        <v>6</v>
+      </c>
+      <c r="P209">
+        <v>-2</v>
+      </c>
+      <c r="Q209">
+        <v>-1</v>
+      </c>
+      <c r="R209">
+        <v>2</v>
+      </c>
+      <c r="S209">
+        <v>-1</v>
+      </c>
+      <c r="T209">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>976</v>
+      </c>
+      <c r="B210">
+        <v>221</v>
+      </c>
+      <c r="C210">
+        <v>5</v>
+      </c>
+      <c r="H210">
+        <v>15554</v>
+      </c>
+      <c r="L210">
+        <v>3878</v>
+      </c>
+      <c r="N210">
+        <v>3</v>
+      </c>
+      <c r="O210">
+        <v>-9</v>
+      </c>
+      <c r="Q210">
+        <v>-3</v>
+      </c>
+      <c r="R210">
+        <v>-11</v>
+      </c>
+      <c r="S210">
+        <v>1</v>
+      </c>
+      <c r="T210">
+        <v>3</v>
+      </c>
+      <c r="U210">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>977</v>
+      </c>
+      <c r="B211">
+        <v>5</v>
+      </c>
+      <c r="C211">
+        <v>32</v>
+      </c>
+      <c r="E211">
+        <v>6512</v>
+      </c>
+      <c r="N211">
+        <v>-3</v>
+      </c>
+      <c r="O211">
+        <v>-1</v>
+      </c>
+      <c r="Q211">
+        <v>-1</v>
+      </c>
+      <c r="R211">
+        <v>3</v>
+      </c>
+      <c r="S211">
+        <v>3</v>
+      </c>
+      <c r="T211">
+        <v>1</v>
+      </c>
+      <c r="U211">
+        <v>-1</v>
+      </c>
+    </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B212">
+        <v>5</v>
+      </c>
+      <c r="C212">
+        <v>5</v>
+      </c>
+      <c r="E212">
+        <v>6935</v>
+      </c>
+      <c r="L212">
+        <v>4548</v>
+      </c>
+      <c r="M212">
+        <v>13023</v>
+      </c>
+      <c r="N212">
+        <v>-11</v>
+      </c>
+      <c r="O212">
+        <v>-8</v>
+      </c>
+      <c r="Q212">
+        <v>-1</v>
+      </c>
+      <c r="R212">
+        <v>1</v>
+      </c>
+      <c r="S212">
+        <v>-6</v>
+      </c>
+      <c r="T212">
+        <v>1</v>
+      </c>
+      <c r="U212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>990</v>
+      </c>
+      <c r="B227">
+        <v>11111</v>
+      </c>
+      <c r="C227">
+        <v>2111</v>
+      </c>
+      <c r="D227">
+        <v>18392</v>
+      </c>
+      <c r="F227">
+        <v>18139</v>
+      </c>
+      <c r="G227">
+        <v>17868</v>
+      </c>
+      <c r="H227">
+        <v>17709</v>
+      </c>
+      <c r="K227">
+        <v>18119</v>
+      </c>
+      <c r="M227">
+        <v>17250</v>
+      </c>
+      <c r="N227">
+        <v>3</v>
+      </c>
+      <c r="O227">
+        <v>10</v>
+      </c>
+      <c r="Q227">
+        <v>0</v>
+      </c>
+      <c r="R227">
+        <v>4</v>
+      </c>
+      <c r="S227">
+        <v>4</v>
+      </c>
+      <c r="T227">
+        <v>3</v>
+      </c>
+      <c r="U227">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>992</v>
+      </c>
+      <c r="B228">
+        <v>311</v>
+      </c>
+      <c r="C228">
         <v>221</v>
       </c>
-      <c r="C212">
-        <v>5</v>
-      </c>
-      <c r="H212">
-        <v>15554</v>
-      </c>
-      <c r="L212">
-        <v>3878</v>
-      </c>
-      <c r="N212">
+      <c r="D228">
+        <v>18380</v>
+      </c>
+      <c r="G228">
+        <v>14981</v>
+      </c>
+      <c r="I228">
+        <v>17842</v>
+      </c>
+      <c r="J228">
+        <v>18630</v>
+      </c>
+      <c r="L228">
+        <v>15117</v>
+      </c>
+      <c r="M228">
+        <v>18260</v>
+      </c>
+      <c r="N228">
+        <v>-3</v>
+      </c>
+      <c r="O228">
+        <v>-1</v>
+      </c>
+      <c r="Q228">
+        <v>-5</v>
+      </c>
+      <c r="R228">
+        <v>2</v>
+      </c>
+      <c r="S228">
+        <v>1</v>
+      </c>
+      <c r="T228">
+        <v>-4</v>
+      </c>
+      <c r="U228">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>999</v>
+      </c>
+      <c r="B235">
+        <v>5</v>
+      </c>
+      <c r="C235">
+        <v>311</v>
+      </c>
+      <c r="D235">
+        <v>4898</v>
+      </c>
+      <c r="E235">
+        <v>3527</v>
+      </c>
+      <c r="G235">
+        <v>4553</v>
+      </c>
+      <c r="I235">
+        <v>6885</v>
+      </c>
+      <c r="J235">
+        <v>6872</v>
+      </c>
+      <c r="K235">
+        <v>8932</v>
+      </c>
+      <c r="M235">
+        <v>9114</v>
+      </c>
+      <c r="N235">
+        <v>-5</v>
+      </c>
+      <c r="O235">
+        <v>1</v>
+      </c>
+      <c r="Q235">
+        <v>-10</v>
+      </c>
+      <c r="R235">
+        <v>7</v>
+      </c>
+      <c r="S235">
         <v>3</v>
       </c>
-      <c r="O212">
-        <v>-9</v>
-      </c>
-      <c r="Q212">
+      <c r="T235">
+        <v>-1</v>
+      </c>
+      <c r="U235">
         <v>-3</v>
       </c>
-      <c r="R212">
-        <v>-11</v>
-      </c>
-      <c r="S212">
-        <v>1</v>
-      </c>
-      <c r="T212">
-        <v>3</v>
-      </c>
-      <c r="U212">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A213">
-        <v>977</v>
-      </c>
-      <c r="B213">
-        <v>5</v>
-      </c>
-      <c r="C213">
-        <v>32</v>
-      </c>
-      <c r="E213">
-        <v>6512</v>
-      </c>
-      <c r="N213">
+    </row>
+    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>1000</v>
+      </c>
+      <c r="B236">
+        <v>5</v>
+      </c>
+      <c r="C236">
+        <v>41</v>
+      </c>
+      <c r="D236">
+        <v>3580</v>
+      </c>
+      <c r="E236">
+        <v>4952</v>
+      </c>
+      <c r="I236">
+        <v>3372</v>
+      </c>
+      <c r="K236">
+        <v>5467</v>
+      </c>
+      <c r="N236">
         <v>-3</v>
       </c>
-      <c r="O213">
-        <v>-1</v>
-      </c>
-      <c r="Q213">
-        <v>-1</v>
-      </c>
-      <c r="R213">
-        <v>3</v>
-      </c>
-      <c r="S213">
-        <v>3</v>
-      </c>
-      <c r="T213">
-        <v>1</v>
-      </c>
-      <c r="U213">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A214">
-        <v>978</v>
-      </c>
-      <c r="B214">
-        <v>5</v>
-      </c>
-      <c r="C214">
-        <v>5</v>
-      </c>
-      <c r="E214">
-        <v>6935</v>
-      </c>
-      <c r="L214">
-        <v>4548</v>
-      </c>
-      <c r="M214">
-        <v>13023</v>
-      </c>
-      <c r="N214">
-        <v>-11</v>
-      </c>
-      <c r="O214">
-        <v>-8</v>
-      </c>
-      <c r="Q214">
-        <v>-1</v>
-      </c>
-      <c r="R214">
-        <v>1</v>
-      </c>
-      <c r="S214">
+      <c r="O236">
+        <v>5</v>
+      </c>
+      <c r="Q236">
+        <v>0</v>
+      </c>
+      <c r="R236">
+        <v>4</v>
+      </c>
+      <c r="S236">
+        <v>2</v>
+      </c>
+      <c r="T236">
         <v>-6</v>
       </c>
-      <c r="T214">
-        <v>1</v>
-      </c>
-      <c r="U214">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A229">
-        <v>990</v>
-      </c>
-      <c r="B229">
-        <v>11111</v>
-      </c>
-      <c r="C229">
-        <v>2111</v>
-      </c>
-      <c r="D229">
-        <v>18392</v>
-      </c>
-      <c r="F229">
-        <v>18139</v>
-      </c>
-      <c r="G229">
-        <v>17868</v>
-      </c>
-      <c r="H229">
-        <v>17709</v>
-      </c>
-      <c r="K229">
-        <v>18119</v>
-      </c>
-      <c r="M229">
-        <v>17250</v>
-      </c>
-      <c r="N229">
-        <v>3</v>
-      </c>
-      <c r="O229">
-        <v>10</v>
-      </c>
-      <c r="Q229">
-        <v>0</v>
-      </c>
-      <c r="R229">
-        <v>4</v>
-      </c>
-      <c r="S229">
-        <v>4</v>
-      </c>
-      <c r="T229">
-        <v>3</v>
-      </c>
-      <c r="U229">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A230">
-        <v>992</v>
-      </c>
-      <c r="B230">
-        <v>311</v>
-      </c>
-      <c r="C230">
-        <v>221</v>
-      </c>
-      <c r="D230">
-        <v>18380</v>
-      </c>
-      <c r="G230">
-        <v>14981</v>
-      </c>
-      <c r="I230">
-        <v>17842</v>
-      </c>
-      <c r="J230">
-        <v>18630</v>
-      </c>
-      <c r="L230">
-        <v>15117</v>
-      </c>
-      <c r="M230">
-        <v>18260</v>
-      </c>
-      <c r="N230">
-        <v>-3</v>
-      </c>
-      <c r="O230">
-        <v>-1</v>
-      </c>
-      <c r="Q230">
-        <v>-5</v>
-      </c>
-      <c r="R230">
-        <v>2</v>
-      </c>
-      <c r="S230">
-        <v>1</v>
-      </c>
-      <c r="T230">
-        <v>-4</v>
-      </c>
-      <c r="U230">
-        <v>-2</v>
+      <c r="U236">
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B237">
         <v>5</v>
       </c>
       <c r="C237">
-        <v>311</v>
+        <v>2111</v>
       </c>
       <c r="D237">
-        <v>4898</v>
-      </c>
-      <c r="E237">
-        <v>3527</v>
-      </c>
-      <c r="G237">
-        <v>4553</v>
-      </c>
-      <c r="I237">
-        <v>6885</v>
+        <v>3704</v>
+      </c>
+      <c r="H237">
+        <v>12528</v>
       </c>
       <c r="J237">
-        <v>6872</v>
+        <v>6609</v>
       </c>
       <c r="K237">
-        <v>8932</v>
+        <v>8845</v>
+      </c>
+      <c r="L237">
+        <v>8091</v>
       </c>
       <c r="M237">
-        <v>9114</v>
+        <v>7545</v>
       </c>
       <c r="N237">
+        <v>-4</v>
+      </c>
+      <c r="O237">
         <v>-5</v>
       </c>
-      <c r="O237">
-        <v>1</v>
-      </c>
       <c r="Q237">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R237">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S237">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="T237">
         <v>-1</v>
       </c>
       <c r="U237">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A238">
-        <v>1000</v>
-      </c>
-      <c r="B238">
-        <v>5</v>
-      </c>
-      <c r="C238">
-        <v>41</v>
-      </c>
-      <c r="D238">
-        <v>3580</v>
-      </c>
-      <c r="E238">
-        <v>4952</v>
-      </c>
-      <c r="I238">
-        <v>3372</v>
-      </c>
-      <c r="K238">
-        <v>5467</v>
-      </c>
-      <c r="N238">
-        <v>-3</v>
-      </c>
-      <c r="O238">
-        <v>5</v>
-      </c>
-      <c r="Q238">
-        <v>0</v>
-      </c>
-      <c r="R238">
-        <v>4</v>
-      </c>
-      <c r="S238">
-        <v>2</v>
-      </c>
-      <c r="T238">
-        <v>-6</v>
-      </c>
-      <c r="U238">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A239">
-        <v>1001</v>
-      </c>
-      <c r="B239">
-        <v>5</v>
-      </c>
-      <c r="C239">
-        <v>2111</v>
-      </c>
-      <c r="D239">
-        <v>3704</v>
-      </c>
-      <c r="H239">
-        <v>12528</v>
-      </c>
-      <c r="J239">
-        <v>6609</v>
-      </c>
-      <c r="K239">
-        <v>8845</v>
-      </c>
-      <c r="L239">
-        <v>8091</v>
-      </c>
-      <c r="M239">
-        <v>7545</v>
-      </c>
-      <c r="N239">
-        <v>-4</v>
-      </c>
-      <c r="O239">
-        <v>-5</v>
-      </c>
-      <c r="Q239">
-        <v>-9</v>
-      </c>
-      <c r="R239">
-        <v>10</v>
-      </c>
-      <c r="S239">
-        <v>-1</v>
-      </c>
-      <c r="T239">
-        <v>-1</v>
-      </c>
-      <c r="U239">
         <v>2</v>
       </c>
     </row>

--- a/datasets/xlsx/CSPreMatchStatistics.xlsx
+++ b/datasets/xlsx/CSPreMatchStatistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D60CA6-D09C-4EBE-9BF5-2A19937B8350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D44235-8715-4AF5-BD66-C00A414971F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U237"/>
+  <dimension ref="A1:U257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -12738,6 +12738,188 @@
         <v>1</v>
       </c>
     </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>979</v>
+      </c>
+      <c r="B213">
+        <v>221</v>
+      </c>
+      <c r="C213">
+        <v>5</v>
+      </c>
+      <c r="D213">
+        <v>19227</v>
+      </c>
+      <c r="F213">
+        <v>18996</v>
+      </c>
+      <c r="G213">
+        <v>18508</v>
+      </c>
+      <c r="N213">
+        <v>3</v>
+      </c>
+      <c r="O213">
+        <v>12</v>
+      </c>
+      <c r="Q213">
+        <v>-4</v>
+      </c>
+      <c r="R213">
+        <v>1</v>
+      </c>
+      <c r="S213">
+        <v>-10</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>980</v>
+      </c>
+      <c r="B214">
+        <v>311</v>
+      </c>
+      <c r="C214">
+        <v>5</v>
+      </c>
+      <c r="D214">
+        <v>22023</v>
+      </c>
+      <c r="I214">
+        <v>22167</v>
+      </c>
+      <c r="L214">
+        <v>19886</v>
+      </c>
+      <c r="M214">
+        <v>23325</v>
+      </c>
+      <c r="N214">
+        <v>-6</v>
+      </c>
+      <c r="O214">
+        <v>-4</v>
+      </c>
+      <c r="Q214">
+        <v>-2</v>
+      </c>
+      <c r="R214">
+        <v>-3</v>
+      </c>
+      <c r="S214">
+        <v>1</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>981</v>
+      </c>
+      <c r="B215">
+        <v>311</v>
+      </c>
+      <c r="C215">
+        <v>221</v>
+      </c>
+      <c r="D215">
+        <v>20878</v>
+      </c>
+      <c r="E215">
+        <v>20470</v>
+      </c>
+      <c r="F215">
+        <v>19629</v>
+      </c>
+      <c r="G215">
+        <v>20111</v>
+      </c>
+      <c r="I215">
+        <v>21944</v>
+      </c>
+      <c r="J215">
+        <v>18265</v>
+      </c>
+      <c r="L215">
+        <v>21754</v>
+      </c>
+      <c r="M215">
+        <v>14998</v>
+      </c>
+      <c r="N215">
+        <v>3</v>
+      </c>
+      <c r="O215">
+        <v>-6</v>
+      </c>
+      <c r="Q215">
+        <v>-4</v>
+      </c>
+      <c r="R215">
+        <v>4</v>
+      </c>
+      <c r="S215">
+        <v>1</v>
+      </c>
+      <c r="T215">
+        <v>1</v>
+      </c>
+      <c r="U215">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>982</v>
+      </c>
+      <c r="B216">
+        <v>5</v>
+      </c>
+      <c r="C216">
+        <v>2111</v>
+      </c>
+      <c r="D216">
+        <v>2833</v>
+      </c>
+      <c r="E216">
+        <v>8603</v>
+      </c>
+      <c r="I216">
+        <v>8662</v>
+      </c>
+      <c r="N216">
+        <v>-6</v>
+      </c>
+      <c r="O216">
+        <v>-2</v>
+      </c>
+      <c r="Q216">
+        <v>3</v>
+      </c>
+      <c r="R216">
+        <v>7</v>
+      </c>
+      <c r="S216">
+        <v>-1</v>
+      </c>
+      <c r="T216">
+        <v>-2</v>
+      </c>
+      <c r="U216">
+        <v>-6</v>
+      </c>
+    </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>990</v>
@@ -12983,6 +13165,94 @@
       </c>
       <c r="U237">
         <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>1022</v>
+      </c>
+      <c r="B256">
+        <v>11111</v>
+      </c>
+      <c r="C256">
+        <v>5</v>
+      </c>
+      <c r="D256">
+        <v>17910</v>
+      </c>
+      <c r="E256">
+        <v>17844</v>
+      </c>
+      <c r="F256">
+        <v>17590</v>
+      </c>
+      <c r="G256">
+        <v>17575</v>
+      </c>
+      <c r="H256">
+        <v>17403</v>
+      </c>
+      <c r="N256">
+        <v>3</v>
+      </c>
+      <c r="O256">
+        <v>12</v>
+      </c>
+      <c r="Q256">
+        <v>4</v>
+      </c>
+      <c r="R256">
+        <v>3</v>
+      </c>
+      <c r="S256">
+        <v>10</v>
+      </c>
+      <c r="T256">
+        <v>3</v>
+      </c>
+      <c r="U256">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>1023</v>
+      </c>
+      <c r="B257">
+        <v>2111</v>
+      </c>
+      <c r="C257">
+        <v>311</v>
+      </c>
+      <c r="D257">
+        <v>11907</v>
+      </c>
+      <c r="G257">
+        <v>10004</v>
+      </c>
+      <c r="H257">
+        <v>10848</v>
+      </c>
+      <c r="N257">
+        <v>6</v>
+      </c>
+      <c r="O257">
+        <v>7</v>
+      </c>
+      <c r="Q257">
+        <v>0</v>
+      </c>
+      <c r="R257">
+        <v>2</v>
+      </c>
+      <c r="S257">
+        <v>2</v>
+      </c>
+      <c r="T257">
+        <v>0</v>
+      </c>
+      <c r="U257">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/xlsx/CSPreMatchStatistics.xlsx
+++ b/datasets/xlsx/CSPreMatchStatistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D44235-8715-4AF5-BD66-C00A414971F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095349FA-CB7D-42E5-B747-34E6F0FE7ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U257"/>
+  <dimension ref="A1:U254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -12920,338 +12920,658 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A227">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>983</v>
+      </c>
+      <c r="B217">
+        <v>5</v>
+      </c>
+      <c r="C217">
+        <v>221</v>
+      </c>
+      <c r="D217">
+        <v>2732</v>
+      </c>
+      <c r="E217">
+        <v>8480</v>
+      </c>
+      <c r="N217">
+        <v>-3</v>
+      </c>
+      <c r="O217">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>1</v>
+      </c>
+      <c r="R217">
+        <v>11</v>
+      </c>
+      <c r="S217">
+        <v>6</v>
+      </c>
+      <c r="T217">
+        <v>-1</v>
+      </c>
+      <c r="U217">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>984</v>
+      </c>
+      <c r="B218">
+        <v>311</v>
+      </c>
+      <c r="C218">
+        <v>221</v>
+      </c>
+      <c r="E218">
+        <v>19025</v>
+      </c>
+      <c r="H218">
+        <v>23148</v>
+      </c>
+      <c r="I218">
+        <v>21036</v>
+      </c>
+      <c r="J218">
+        <v>19308</v>
+      </c>
+      <c r="K218">
+        <v>19999</v>
+      </c>
+      <c r="L218">
+        <v>19999</v>
+      </c>
+      <c r="N218">
+        <v>-5</v>
+      </c>
+      <c r="O218">
+        <v>-4</v>
+      </c>
+      <c r="Q218">
+        <v>-1</v>
+      </c>
+      <c r="R218">
+        <v>5</v>
+      </c>
+      <c r="S218">
+        <v>4</v>
+      </c>
+      <c r="T218">
+        <v>-1</v>
+      </c>
+      <c r="U218">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>985</v>
+      </c>
+      <c r="B219">
+        <v>311</v>
+      </c>
+      <c r="C219">
+        <v>311</v>
+      </c>
+      <c r="F219">
+        <v>25760</v>
+      </c>
+      <c r="H219">
+        <v>22873</v>
+      </c>
+      <c r="K219">
+        <v>24295</v>
+      </c>
+      <c r="L219">
+        <v>19890</v>
+      </c>
+      <c r="M219">
+        <v>24609</v>
+      </c>
+      <c r="N219">
+        <v>-6</v>
+      </c>
+      <c r="O219">
+        <v>-11</v>
+      </c>
+      <c r="Q219">
+        <v>0</v>
+      </c>
+      <c r="R219">
+        <v>-1</v>
+      </c>
+      <c r="S219">
+        <v>0</v>
+      </c>
+      <c r="T219">
+        <v>-1</v>
+      </c>
+      <c r="U219">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>986</v>
+      </c>
+      <c r="B220">
+        <v>2111</v>
+      </c>
+      <c r="C220">
+        <v>5</v>
+      </c>
+      <c r="D220">
+        <v>19963</v>
+      </c>
+      <c r="E220">
+        <v>19617</v>
+      </c>
+      <c r="I220">
+        <v>18373</v>
+      </c>
+      <c r="J220">
+        <v>22569</v>
+      </c>
+      <c r="K220">
+        <v>18918</v>
+      </c>
+      <c r="L220">
+        <v>18907</v>
+      </c>
+      <c r="N220">
+        <v>-1</v>
+      </c>
+      <c r="O220">
+        <v>-9</v>
+      </c>
+      <c r="Q220">
+        <v>-7</v>
+      </c>
+      <c r="R220">
+        <v>3</v>
+      </c>
+      <c r="S220">
+        <v>-2</v>
+      </c>
+      <c r="T220">
+        <v>1</v>
+      </c>
+      <c r="U220">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>987</v>
+      </c>
+      <c r="B221">
+        <v>2111</v>
+      </c>
+      <c r="C221">
+        <v>5</v>
+      </c>
+      <c r="F221">
+        <v>18151</v>
+      </c>
+      <c r="I221">
+        <v>18394</v>
+      </c>
+      <c r="J221">
+        <v>14473</v>
+      </c>
+      <c r="K221">
+        <v>18151</v>
+      </c>
+      <c r="M221">
+        <v>18698</v>
+      </c>
+      <c r="N221">
+        <v>-5</v>
+      </c>
+      <c r="O221">
+        <v>-19</v>
+      </c>
+      <c r="Q221">
+        <v>2</v>
+      </c>
+      <c r="R221">
+        <v>1</v>
+      </c>
+      <c r="S221">
+        <v>5</v>
+      </c>
+      <c r="T221">
+        <v>-3</v>
+      </c>
+      <c r="U221">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>988</v>
+      </c>
+      <c r="B222">
+        <v>2111</v>
+      </c>
+      <c r="C222">
+        <v>5</v>
+      </c>
+      <c r="E222">
+        <v>17864</v>
+      </c>
+      <c r="F222">
+        <v>17648</v>
+      </c>
+      <c r="N222">
+        <v>4</v>
+      </c>
+      <c r="O222">
+        <v>-9</v>
+      </c>
+      <c r="Q222">
+        <v>6</v>
+      </c>
+      <c r="R222">
+        <v>9</v>
+      </c>
+      <c r="S222">
+        <v>2</v>
+      </c>
+      <c r="T222">
+        <v>-8</v>
+      </c>
+      <c r="U222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>989</v>
+      </c>
+      <c r="B223">
+        <v>2111</v>
+      </c>
+      <c r="C223">
+        <v>221</v>
+      </c>
+      <c r="D223">
+        <v>17942</v>
+      </c>
+      <c r="E223">
+        <v>17760</v>
+      </c>
+      <c r="G223">
+        <v>18543</v>
+      </c>
+      <c r="H223">
+        <v>15000</v>
+      </c>
+      <c r="I223">
+        <v>18000</v>
+      </c>
+      <c r="J223">
+        <v>16902</v>
+      </c>
+      <c r="N223">
+        <v>7</v>
+      </c>
+      <c r="O223">
+        <v>4</v>
+      </c>
+      <c r="Q223">
+        <v>0</v>
+      </c>
+      <c r="R223">
+        <v>-3</v>
+      </c>
+      <c r="S223">
+        <v>9</v>
+      </c>
+      <c r="T223">
+        <v>-3</v>
+      </c>
+      <c r="U223">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A224">
         <v>990</v>
       </c>
-      <c r="B227">
+      <c r="B224">
         <v>11111</v>
       </c>
-      <c r="C227">
+      <c r="C224">
         <v>2111</v>
       </c>
-      <c r="D227">
+      <c r="D224">
         <v>18392</v>
       </c>
-      <c r="F227">
+      <c r="F224">
         <v>18139</v>
       </c>
-      <c r="G227">
+      <c r="G224">
         <v>17868</v>
       </c>
-      <c r="H227">
+      <c r="H224">
         <v>17709</v>
       </c>
-      <c r="K227">
+      <c r="K224">
         <v>18119</v>
       </c>
-      <c r="M227">
+      <c r="M224">
         <v>17250</v>
       </c>
-      <c r="N227">
+      <c r="N224">
         <v>3</v>
       </c>
-      <c r="O227">
+      <c r="O224">
         <v>10</v>
       </c>
-      <c r="Q227">
-        <v>0</v>
-      </c>
-      <c r="R227">
+      <c r="Q224">
+        <v>0</v>
+      </c>
+      <c r="R224">
         <v>4</v>
       </c>
-      <c r="S227">
+      <c r="S224">
         <v>4</v>
       </c>
-      <c r="T227">
+      <c r="T224">
         <v>3</v>
       </c>
-      <c r="U227">
+      <c r="U224">
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A228">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A225">
         <v>992</v>
       </c>
-      <c r="B228">
+      <c r="B225">
         <v>311</v>
       </c>
-      <c r="C228">
+      <c r="C225">
         <v>221</v>
       </c>
-      <c r="D228">
+      <c r="D225">
         <v>18380</v>
       </c>
-      <c r="G228">
+      <c r="G225">
         <v>14981</v>
       </c>
-      <c r="I228">
+      <c r="I225">
         <v>17842</v>
       </c>
-      <c r="J228">
+      <c r="J225">
         <v>18630</v>
       </c>
-      <c r="L228">
+      <c r="L225">
         <v>15117</v>
       </c>
-      <c r="M228">
+      <c r="M225">
         <v>18260</v>
       </c>
-      <c r="N228">
+      <c r="N225">
         <v>-3</v>
       </c>
-      <c r="O228">
+      <c r="O225">
         <v>-1</v>
       </c>
-      <c r="Q228">
+      <c r="Q225">
         <v>-5</v>
       </c>
-      <c r="R228">
+      <c r="R225">
         <v>2</v>
       </c>
-      <c r="S228">
+      <c r="S225">
         <v>1</v>
       </c>
-      <c r="T228">
+      <c r="T225">
         <v>-4</v>
       </c>
-      <c r="U228">
+      <c r="U225">
         <v>-2</v>
       </c>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A235">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A232">
         <v>999</v>
       </c>
-      <c r="B235">
-        <v>5</v>
-      </c>
-      <c r="C235">
+      <c r="B232">
+        <v>5</v>
+      </c>
+      <c r="C232">
         <v>311</v>
       </c>
-      <c r="D235">
+      <c r="D232">
         <v>4898</v>
       </c>
-      <c r="E235">
+      <c r="E232">
         <v>3527</v>
       </c>
-      <c r="G235">
+      <c r="G232">
         <v>4553</v>
       </c>
-      <c r="I235">
+      <c r="I232">
         <v>6885</v>
       </c>
-      <c r="J235">
+      <c r="J232">
         <v>6872</v>
       </c>
-      <c r="K235">
+      <c r="K232">
         <v>8932</v>
       </c>
-      <c r="M235">
+      <c r="M232">
         <v>9114</v>
       </c>
-      <c r="N235">
+      <c r="N232">
         <v>-5</v>
       </c>
-      <c r="O235">
+      <c r="O232">
         <v>1</v>
       </c>
-      <c r="Q235">
+      <c r="Q232">
         <v>-10</v>
       </c>
-      <c r="R235">
+      <c r="R232">
         <v>7</v>
       </c>
-      <c r="S235">
+      <c r="S232">
         <v>3</v>
       </c>
-      <c r="T235">
+      <c r="T232">
         <v>-1</v>
       </c>
-      <c r="U235">
+      <c r="U232">
         <v>-3</v>
       </c>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A236">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A233">
         <v>1000</v>
       </c>
-      <c r="B236">
-        <v>5</v>
-      </c>
-      <c r="C236">
+      <c r="B233">
+        <v>5</v>
+      </c>
+      <c r="C233">
         <v>41</v>
       </c>
-      <c r="D236">
+      <c r="D233">
         <v>3580</v>
       </c>
-      <c r="E236">
+      <c r="E233">
         <v>4952</v>
       </c>
-      <c r="I236">
+      <c r="I233">
         <v>3372</v>
       </c>
-      <c r="K236">
+      <c r="K233">
         <v>5467</v>
       </c>
-      <c r="N236">
+      <c r="N233">
         <v>-3</v>
       </c>
-      <c r="O236">
-        <v>5</v>
-      </c>
-      <c r="Q236">
-        <v>0</v>
-      </c>
-      <c r="R236">
+      <c r="O233">
+        <v>5</v>
+      </c>
+      <c r="Q233">
+        <v>0</v>
+      </c>
+      <c r="R233">
         <v>4</v>
       </c>
-      <c r="S236">
+      <c r="S233">
         <v>2</v>
       </c>
-      <c r="T236">
+      <c r="T233">
         <v>-6</v>
       </c>
-      <c r="U236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A237">
+      <c r="U233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A234">
         <v>1001</v>
       </c>
-      <c r="B237">
-        <v>5</v>
-      </c>
-      <c r="C237">
+      <c r="B234">
+        <v>5</v>
+      </c>
+      <c r="C234">
         <v>2111</v>
       </c>
-      <c r="D237">
+      <c r="D234">
         <v>3704</v>
       </c>
-      <c r="H237">
+      <c r="H234">
         <v>12528</v>
       </c>
-      <c r="J237">
+      <c r="J234">
         <v>6609</v>
       </c>
-      <c r="K237">
+      <c r="K234">
         <v>8845</v>
       </c>
-      <c r="L237">
+      <c r="L234">
         <v>8091</v>
       </c>
-      <c r="M237">
+      <c r="M234">
         <v>7545</v>
       </c>
-      <c r="N237">
+      <c r="N234">
         <v>-4</v>
       </c>
-      <c r="O237">
+      <c r="O234">
         <v>-5</v>
       </c>
-      <c r="Q237">
+      <c r="Q234">
         <v>-9</v>
       </c>
-      <c r="R237">
+      <c r="R234">
         <v>10</v>
       </c>
-      <c r="S237">
+      <c r="S234">
         <v>-1</v>
       </c>
-      <c r="T237">
+      <c r="T234">
         <v>-1</v>
       </c>
-      <c r="U237">
+      <c r="U234">
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A256">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A253">
         <v>1022</v>
       </c>
-      <c r="B256">
+      <c r="B253">
         <v>11111</v>
       </c>
-      <c r="C256">
-        <v>5</v>
-      </c>
-      <c r="D256">
+      <c r="C253">
+        <v>5</v>
+      </c>
+      <c r="D253">
         <v>17910</v>
       </c>
-      <c r="E256">
+      <c r="E253">
         <v>17844</v>
       </c>
-      <c r="F256">
+      <c r="F253">
         <v>17590</v>
       </c>
-      <c r="G256">
+      <c r="G253">
         <v>17575</v>
       </c>
-      <c r="H256">
+      <c r="H253">
         <v>17403</v>
       </c>
-      <c r="N256">
+      <c r="N253">
         <v>3</v>
       </c>
-      <c r="O256">
+      <c r="O253">
         <v>12</v>
       </c>
-      <c r="Q256">
+      <c r="Q253">
         <v>4</v>
       </c>
-      <c r="R256">
+      <c r="R253">
         <v>3</v>
       </c>
-      <c r="S256">
+      <c r="S253">
         <v>10</v>
       </c>
-      <c r="T256">
+      <c r="T253">
         <v>3</v>
       </c>
-      <c r="U256">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A257">
+      <c r="U253">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A254">
         <v>1023</v>
       </c>
-      <c r="B257">
+      <c r="B254">
         <v>2111</v>
       </c>
-      <c r="C257">
+      <c r="C254">
         <v>311</v>
       </c>
-      <c r="D257">
+      <c r="D254">
         <v>11907</v>
       </c>
-      <c r="G257">
+      <c r="G254">
         <v>10004</v>
       </c>
-      <c r="H257">
+      <c r="H254">
         <v>10848</v>
       </c>
-      <c r="N257">
+      <c r="N254">
         <v>6</v>
       </c>
-      <c r="O257">
+      <c r="O254">
         <v>7</v>
       </c>
-      <c r="Q257">
-        <v>0</v>
-      </c>
-      <c r="R257">
+      <c r="Q254">
+        <v>0</v>
+      </c>
+      <c r="R254">
         <v>2</v>
       </c>
-      <c r="S257">
+      <c r="S254">
         <v>2</v>
       </c>
-      <c r="T257">
-        <v>0</v>
-      </c>
-      <c r="U257">
+      <c r="T254">
+        <v>0</v>
+      </c>
+      <c r="U254">
         <v>4</v>
       </c>
     </row>

--- a/datasets/xlsx/CSPreMatchStatistics.xlsx
+++ b/datasets/xlsx/CSPreMatchStatistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095349FA-CB7D-42E5-B747-34E6F0FE7ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A828B65-F8CD-4F85-BEF4-E3FC9570BEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U254"/>
+  <dimension ref="A1:U264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -13340,6 +13340,215 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>993</v>
+      </c>
+      <c r="B226">
+        <v>5</v>
+      </c>
+      <c r="C226">
+        <v>11111</v>
+      </c>
+      <c r="D226">
+        <v>11506</v>
+      </c>
+      <c r="G226">
+        <v>8674</v>
+      </c>
+      <c r="H226">
+        <v>2825</v>
+      </c>
+      <c r="I226">
+        <v>8663</v>
+      </c>
+      <c r="J226">
+        <v>9894</v>
+      </c>
+      <c r="L226">
+        <v>7548</v>
+      </c>
+      <c r="M226">
+        <v>8604</v>
+      </c>
+      <c r="N226">
+        <v>-4</v>
+      </c>
+      <c r="O226">
+        <v>-6</v>
+      </c>
+      <c r="Q226">
+        <v>1</v>
+      </c>
+      <c r="R226">
+        <v>7</v>
+      </c>
+      <c r="S226">
+        <v>-3</v>
+      </c>
+      <c r="T226">
+        <v>-2</v>
+      </c>
+      <c r="U226">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>994</v>
+      </c>
+      <c r="B227">
+        <v>5</v>
+      </c>
+      <c r="C227">
+        <v>2111</v>
+      </c>
+      <c r="D227">
+        <v>11404</v>
+      </c>
+      <c r="G227">
+        <v>8250</v>
+      </c>
+      <c r="H227">
+        <v>2703</v>
+      </c>
+      <c r="K227">
+        <v>8558</v>
+      </c>
+      <c r="L227">
+        <v>8375</v>
+      </c>
+      <c r="M227">
+        <v>7079</v>
+      </c>
+      <c r="N227">
+        <v>-2</v>
+      </c>
+      <c r="O227">
+        <v>-12</v>
+      </c>
+      <c r="Q227">
+        <v>-2</v>
+      </c>
+      <c r="R227">
+        <v>6</v>
+      </c>
+      <c r="S227">
+        <v>-2</v>
+      </c>
+      <c r="T227">
+        <v>1</v>
+      </c>
+      <c r="U227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>995</v>
+      </c>
+      <c r="B228">
+        <v>5</v>
+      </c>
+      <c r="C228">
+        <v>41</v>
+      </c>
+      <c r="D228">
+        <v>11290</v>
+      </c>
+      <c r="G228">
+        <v>7828</v>
+      </c>
+      <c r="H228">
+        <v>2584</v>
+      </c>
+      <c r="I228">
+        <v>8239</v>
+      </c>
+      <c r="J228">
+        <v>5901</v>
+      </c>
+      <c r="K228">
+        <v>6869</v>
+      </c>
+      <c r="M228">
+        <v>9636</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228">
+        <v>-11</v>
+      </c>
+      <c r="Q228">
+        <v>1</v>
+      </c>
+      <c r="R228">
+        <v>5</v>
+      </c>
+      <c r="S228">
+        <v>4</v>
+      </c>
+      <c r="T228">
+        <v>-8</v>
+      </c>
+      <c r="U228">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>996</v>
+      </c>
+      <c r="B229">
+        <v>311</v>
+      </c>
+      <c r="C229">
+        <v>32</v>
+      </c>
+      <c r="D229">
+        <v>17740</v>
+      </c>
+      <c r="E229">
+        <v>19106</v>
+      </c>
+      <c r="I229">
+        <v>18638</v>
+      </c>
+      <c r="J229">
+        <v>17338</v>
+      </c>
+      <c r="K229">
+        <v>17955</v>
+      </c>
+      <c r="L229">
+        <v>14680</v>
+      </c>
+      <c r="M229">
+        <v>17935</v>
+      </c>
+      <c r="N229">
+        <v>-2</v>
+      </c>
+      <c r="O229">
+        <v>-10</v>
+      </c>
+      <c r="Q229">
+        <v>2</v>
+      </c>
+      <c r="R229">
+        <v>-5</v>
+      </c>
+      <c r="S229">
+        <v>3</v>
+      </c>
+      <c r="T229">
+        <v>-5</v>
+      </c>
+      <c r="U229">
+        <v>-4</v>
+      </c>
+    </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>999</v>
@@ -13573,6 +13782,41 @@
       </c>
       <c r="U254">
         <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>1033</v>
+      </c>
+      <c r="B264">
+        <v>2111</v>
+      </c>
+      <c r="C264">
+        <v>2111</v>
+      </c>
+      <c r="H264">
+        <v>10852</v>
+      </c>
+      <c r="N264">
+        <v>-1</v>
+      </c>
+      <c r="O264">
+        <v>-1</v>
+      </c>
+      <c r="Q264">
+        <v>13</v>
+      </c>
+      <c r="R264">
+        <v>2</v>
+      </c>
+      <c r="S264">
+        <v>2</v>
+      </c>
+      <c r="T264">
+        <v>0</v>
+      </c>
+      <c r="U264">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
